--- a/research/traditional_assets/database/data/austria/austria_computers_peripherals.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_computers_peripherals.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1064439603335769</v>
+        <v>0.1062226948287763</v>
       </c>
       <c r="C2">
-        <v>326.9831380159191</v>
+        <v>324.4175657457021</v>
       </c>
       <c r="D2">
-        <v>299.6831380159191</v>
+        <v>300.7805657457021</v>
       </c>
       <c r="E2">
-        <v>-143.3</v>
+        <v>-139.637</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.663</v>
       </c>
       <c r="G2">
         <v>27.3</v>
@@ -1445,28 +1445,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1842489</v>
       </c>
       <c r="N2">
-        <v>40.71111111111111</v>
+        <v>40.52686221111111</v>
       </c>
       <c r="O2">
-        <v>9.770666666666665</v>
+        <v>9.726446930666667</v>
       </c>
       <c r="P2">
-        <v>30.94044444444445</v>
+        <v>30.80041528044444</v>
       </c>
       <c r="Q2">
-        <v>41.34044444444444</v>
+        <v>41.20041528044444</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1064439603335769</v>
+        <v>0.1069095099280569</v>
       </c>
       <c r="T2">
-        <v>1.246903653332528</v>
+        <v>1.256475842994475</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>220.9571460731169</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1062226948287763</v>
+        <v>0.1060014293239757</v>
       </c>
       <c r="C3">
-        <v>324.4175657457021</v>
+        <v>321.8600604899511</v>
       </c>
       <c r="D3">
-        <v>300.7805657457021</v>
+        <v>301.8860604899511</v>
       </c>
       <c r="E3">
-        <v>-139.637</v>
+        <v>-135.974</v>
       </c>
       <c r="F3">
-        <v>3.663</v>
+        <v>7.326000000000001</v>
       </c>
       <c r="G3">
         <v>27.3</v>
@@ -1527,28 +1527,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M3">
-        <v>0.1842489</v>
+        <v>0.3684978</v>
       </c>
       <c r="N3">
-        <v>40.52686221111111</v>
+        <v>40.34261331111111</v>
       </c>
       <c r="O3">
-        <v>9.726446930666667</v>
+        <v>9.682227194666666</v>
       </c>
       <c r="P3">
-        <v>30.80041528044444</v>
+        <v>30.66038611644444</v>
       </c>
       <c r="Q3">
-        <v>41.20041528044444</v>
+        <v>41.06038611644444</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1069095099280569</v>
+        <v>0.1073845605346691</v>
       </c>
       <c r="T3">
-        <v>1.256475842994475</v>
+        <v>1.266243383465849</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>220.9571460731169</v>
+        <v>110.4785730365585</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1060014293239757</v>
+        <v>0.1057801638191752</v>
       </c>
       <c r="C4">
-        <v>321.8600604899511</v>
+        <v>319.3107115257826</v>
       </c>
       <c r="D4">
-        <v>301.8860604899511</v>
+        <v>302.9997115257825</v>
       </c>
       <c r="E4">
-        <v>-135.974</v>
+        <v>-132.311</v>
       </c>
       <c r="F4">
-        <v>7.326000000000001</v>
+        <v>10.989</v>
       </c>
       <c r="G4">
         <v>27.3</v>
@@ -1609,28 +1609,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M4">
-        <v>0.3684978</v>
+        <v>0.5527467</v>
       </c>
       <c r="N4">
-        <v>40.34261331111111</v>
+        <v>40.15836441111111</v>
       </c>
       <c r="O4">
-        <v>9.682227194666666</v>
+        <v>9.638007458666666</v>
       </c>
       <c r="P4">
-        <v>30.66038611644444</v>
+        <v>30.52035695244444</v>
       </c>
       <c r="Q4">
-        <v>41.06038611644444</v>
+        <v>40.92035695244444</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1073845605346691</v>
+        <v>0.1078694059991497</v>
       </c>
       <c r="T4">
-        <v>1.266243383465849</v>
+        <v>1.276212316524262</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>110.4785730365585</v>
+        <v>73.6523820243723</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1057801638191752</v>
+        <v>0.1055588983143746</v>
       </c>
       <c r="C5">
-        <v>319.3107115257826</v>
+        <v>316.7696094525563</v>
       </c>
       <c r="D5">
-        <v>302.9997115257825</v>
+        <v>304.1216094525562</v>
       </c>
       <c r="E5">
-        <v>-132.311</v>
+        <v>-128.648</v>
       </c>
       <c r="F5">
-        <v>10.989</v>
+        <v>14.652</v>
       </c>
       <c r="G5">
         <v>27.3</v>
@@ -1691,28 +1691,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M5">
-        <v>0.5527467</v>
+        <v>0.7369956</v>
       </c>
       <c r="N5">
-        <v>40.15836441111111</v>
+        <v>39.97411551111111</v>
       </c>
       <c r="O5">
-        <v>9.638007458666666</v>
+        <v>9.593787722666665</v>
       </c>
       <c r="P5">
-        <v>30.52035695244444</v>
+        <v>30.38032778844444</v>
       </c>
       <c r="Q5">
-        <v>40.92035695244444</v>
+        <v>40.78032778844444</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1078694059991497</v>
+        <v>0.1083643524108069</v>
       </c>
       <c r="T5">
-        <v>1.276212316524262</v>
+        <v>1.286388935688058</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>73.6523820243723</v>
+        <v>55.23928651827923</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1055588983143746</v>
+        <v>0.105337632809574</v>
       </c>
       <c r="C6">
-        <v>316.7696094525563</v>
+        <v>314.236846216445</v>
       </c>
       <c r="D6">
-        <v>304.1216094525562</v>
+        <v>305.251846216445</v>
       </c>
       <c r="E6">
-        <v>-128.648</v>
+        <v>-124.985</v>
       </c>
       <c r="F6">
-        <v>14.652</v>
+        <v>18.315</v>
       </c>
       <c r="G6">
         <v>27.3</v>
@@ -1773,28 +1773,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M6">
-        <v>0.7369956</v>
+        <v>0.9212445</v>
       </c>
       <c r="N6">
-        <v>39.97411551111111</v>
+        <v>39.78986661111111</v>
       </c>
       <c r="O6">
-        <v>9.593787722666665</v>
+        <v>9.549567986666666</v>
       </c>
       <c r="P6">
-        <v>30.38032778844444</v>
+        <v>30.24029862444444</v>
       </c>
       <c r="Q6">
-        <v>40.78032778844444</v>
+        <v>40.64029862444444</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1083643524108069</v>
+        <v>0.10886971874692</v>
       </c>
       <c r="T6">
-        <v>1.286388935688058</v>
+        <v>1.296779799465829</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>55.23928651827923</v>
+        <v>44.19142921462338</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.105337632809574</v>
+        <v>0.1051163673047734</v>
       </c>
       <c r="C7">
-        <v>314.236846216445</v>
+        <v>311.7125151355539</v>
       </c>
       <c r="D7">
-        <v>305.251846216445</v>
+        <v>306.3905151355539</v>
       </c>
       <c r="E7">
-        <v>-124.985</v>
+        <v>-121.322</v>
       </c>
       <c r="F7">
-        <v>18.315</v>
+        <v>21.978</v>
       </c>
       <c r="G7">
         <v>27.3</v>
@@ -1855,28 +1855,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M7">
-        <v>0.9212445</v>
+        <v>1.1054934</v>
       </c>
       <c r="N7">
-        <v>39.78986661111111</v>
+        <v>39.60561771111111</v>
       </c>
       <c r="O7">
-        <v>9.549567986666666</v>
+        <v>9.505348250666666</v>
       </c>
       <c r="P7">
-        <v>30.24029862444444</v>
+        <v>30.10026946044444</v>
       </c>
       <c r="Q7">
-        <v>40.64029862444444</v>
+        <v>40.50026946044444</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.10886971874692</v>
+        <v>0.1093858375582696</v>
       </c>
       <c r="T7">
-        <v>1.296779799465829</v>
+        <v>1.307391745451638</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>44.19142921462338</v>
+        <v>36.82619101218615</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1051163673047734</v>
+        <v>0.1048951017999729</v>
       </c>
       <c r="C8">
-        <v>311.7125151355539</v>
+        <v>309.1967109256051</v>
       </c>
       <c r="D8">
-        <v>306.3905151355539</v>
+        <v>307.5377109256051</v>
       </c>
       <c r="E8">
-        <v>-121.322</v>
+        <v>-117.659</v>
       </c>
       <c r="F8">
-        <v>21.978</v>
+        <v>25.641</v>
       </c>
       <c r="G8">
         <v>27.3</v>
@@ -1937,28 +1937,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M8">
-        <v>1.1054934</v>
+        <v>1.2897423</v>
       </c>
       <c r="N8">
-        <v>39.60561771111111</v>
+        <v>39.42136881111111</v>
       </c>
       <c r="O8">
-        <v>9.505348250666666</v>
+        <v>9.461128514666665</v>
       </c>
       <c r="P8">
-        <v>30.10026946044444</v>
+        <v>29.96024029644444</v>
       </c>
       <c r="Q8">
-        <v>40.50026946044444</v>
+        <v>40.36024029644445</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1093858375582696</v>
+        <v>0.1099130556988955</v>
       </c>
       <c r="T8">
-        <v>1.307391745451638</v>
+        <v>1.318231905329614</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.82619101218615</v>
+        <v>31.56530658187384</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1048951017999728</v>
+        <v>0.1046738362951723</v>
       </c>
       <c r="C9">
-        <v>309.1967109256051</v>
+        <v>306.6895297262012</v>
       </c>
       <c r="D9">
-        <v>307.5377109256052</v>
+        <v>308.6935297262011</v>
       </c>
       <c r="E9">
-        <v>-117.659</v>
+        <v>-113.996</v>
       </c>
       <c r="F9">
-        <v>25.641</v>
+        <v>29.304</v>
       </c>
       <c r="G9">
         <v>27.3</v>
@@ -2019,28 +2019,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M9">
-        <v>1.2897423</v>
+        <v>1.4739912</v>
       </c>
       <c r="N9">
-        <v>39.42136881111111</v>
+        <v>39.23711991111111</v>
       </c>
       <c r="O9">
-        <v>9.461128514666665</v>
+        <v>9.416908778666665</v>
       </c>
       <c r="P9">
-        <v>29.96024029644444</v>
+        <v>29.82021113244444</v>
       </c>
       <c r="Q9">
-        <v>40.36024029644445</v>
+        <v>40.22021113244444</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1099130556988955</v>
+        <v>0.1104517351034481</v>
       </c>
       <c r="T9">
-        <v>1.318231905329614</v>
+        <v>1.329307720857112</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.56530658187384</v>
+        <v>27.61964325913961</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1046738362951723</v>
+        <v>0.1044525707903717</v>
       </c>
       <c r="C10">
-        <v>306.6895297262012</v>
+        <v>304.1910691276822</v>
       </c>
       <c r="D10">
-        <v>308.6935297262011</v>
+        <v>309.8580691276821</v>
       </c>
       <c r="E10">
-        <v>-113.996</v>
+        <v>-110.333</v>
       </c>
       <c r="F10">
-        <v>29.304</v>
+        <v>32.967</v>
       </c>
       <c r="G10">
         <v>27.3</v>
@@ -2101,28 +2101,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M10">
-        <v>1.4739912</v>
+        <v>1.6582401</v>
       </c>
       <c r="N10">
-        <v>39.23711991111111</v>
+        <v>39.05287101111111</v>
       </c>
       <c r="O10">
-        <v>9.416908778666665</v>
+        <v>9.372689042666666</v>
       </c>
       <c r="P10">
-        <v>29.82021113244444</v>
+        <v>29.68018196844444</v>
       </c>
       <c r="Q10">
-        <v>40.22021113244444</v>
+        <v>40.08018196844444</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1104517351034481</v>
+        <v>0.1110022536157931</v>
       </c>
       <c r="T10">
-        <v>1.329307720857112</v>
+        <v>1.340626960901698</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.61964325913961</v>
+        <v>24.5507940081241</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1044525707903717</v>
+        <v>0.1042313052855711</v>
       </c>
       <c r="C11">
-        <v>304.1910691276822</v>
+        <v>301.7014281985944</v>
       </c>
       <c r="D11">
-        <v>309.8580691276821</v>
+        <v>311.0314281985944</v>
       </c>
       <c r="E11">
-        <v>-110.333</v>
+        <v>-106.67</v>
       </c>
       <c r="F11">
-        <v>32.967</v>
+        <v>36.63</v>
       </c>
       <c r="G11">
         <v>27.3</v>
@@ -2183,28 +2183,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M11">
-        <v>1.6582401</v>
+        <v>1.842489</v>
       </c>
       <c r="N11">
-        <v>39.05287101111111</v>
+        <v>38.86862211111111</v>
       </c>
       <c r="O11">
-        <v>9.372689042666666</v>
+        <v>9.328469306666666</v>
       </c>
       <c r="P11">
-        <v>29.68018196844444</v>
+        <v>29.54015280444444</v>
       </c>
       <c r="Q11">
-        <v>40.08018196844444</v>
+        <v>39.94015280444444</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1110022536157931</v>
+        <v>0.1115650058728568</v>
       </c>
       <c r="T11">
-        <v>1.340626960901698</v>
+        <v>1.352197739613942</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.5507940081241</v>
+        <v>22.0957146073117</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1042313052855711</v>
+        <v>0.1040100397807705</v>
       </c>
       <c r="C12">
-        <v>301.7014281985944</v>
+        <v>299.2207075137848</v>
       </c>
       <c r="D12">
-        <v>311.0314281985944</v>
+        <v>312.2137075137848</v>
       </c>
       <c r="E12">
-        <v>-106.67</v>
+        <v>-103.007</v>
       </c>
       <c r="F12">
-        <v>36.63</v>
+        <v>40.293</v>
       </c>
       <c r="G12">
         <v>27.3</v>
@@ -2265,28 +2265,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M12">
-        <v>1.842489</v>
+        <v>2.0267379</v>
       </c>
       <c r="N12">
-        <v>38.86862211111111</v>
+        <v>38.68437321111111</v>
       </c>
       <c r="O12">
-        <v>9.328469306666666</v>
+        <v>9.284249570666665</v>
       </c>
       <c r="P12">
-        <v>29.54015280444444</v>
+        <v>29.40012364044444</v>
       </c>
       <c r="Q12">
-        <v>39.94015280444444</v>
+        <v>39.80012364044444</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1115650058728568</v>
+        <v>0.1121404042480567</v>
       </c>
       <c r="T12">
-        <v>1.352197739613942</v>
+        <v>1.364028535825336</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.09571460731169</v>
+        <v>20.08701327937427</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1040100397807705</v>
+        <v>0.1037887742759699</v>
       </c>
       <c r="C13">
-        <v>299.2207075137848</v>
+        <v>296.7490091831378</v>
       </c>
       <c r="D13">
-        <v>312.2137075137848</v>
+        <v>313.4050091831378</v>
       </c>
       <c r="E13">
-        <v>-103.007</v>
+        <v>-99.34400000000001</v>
       </c>
       <c r="F13">
-        <v>40.293</v>
+        <v>43.956</v>
       </c>
       <c r="G13">
         <v>27.3</v>
@@ -2347,28 +2347,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M13">
-        <v>2.0267379</v>
+        <v>2.2109868</v>
       </c>
       <c r="N13">
-        <v>38.68437321111111</v>
+        <v>38.50012431111111</v>
       </c>
       <c r="O13">
-        <v>9.284249570666665</v>
+        <v>9.240029834666666</v>
       </c>
       <c r="P13">
-        <v>29.40012364044444</v>
+        <v>29.26009447644444</v>
       </c>
       <c r="Q13">
-        <v>39.80012364044444</v>
+        <v>39.66009447644444</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1121404042480567</v>
+        <v>0.1127288798590567</v>
       </c>
       <c r="T13">
-        <v>1.364028535825336</v>
+        <v>1.376128213768808</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.08701327937427</v>
+        <v>18.41309550609308</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1037887742759699</v>
+        <v>0.1035675087711693</v>
       </c>
       <c r="C14">
-        <v>296.7490091831378</v>
+        <v>294.2864368809746</v>
       </c>
       <c r="D14">
-        <v>313.4050091831378</v>
+        <v>314.6054368809746</v>
       </c>
       <c r="E14">
-        <v>-99.34400000000001</v>
+        <v>-95.68100000000001</v>
       </c>
       <c r="F14">
-        <v>43.956</v>
+        <v>47.619</v>
       </c>
       <c r="G14">
         <v>27.3</v>
@@ -2429,28 +2429,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M14">
-        <v>2.2109868</v>
+        <v>2.3952357</v>
       </c>
       <c r="N14">
-        <v>38.50012431111111</v>
+        <v>38.31587541111111</v>
       </c>
       <c r="O14">
-        <v>9.240029834666666</v>
+        <v>9.195810098666666</v>
       </c>
       <c r="P14">
-        <v>29.26009447644444</v>
+        <v>29.12006531244444</v>
       </c>
       <c r="Q14">
-        <v>39.66009447644444</v>
+        <v>39.52006531244444</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1127288798590567</v>
+        <v>0.1133308836450222</v>
       </c>
       <c r="T14">
-        <v>1.376128213768808</v>
+        <v>1.388506045228222</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.41309550609308</v>
+        <v>16.99670354408592</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1035675087711693</v>
+        <v>0.1033462432663687</v>
       </c>
       <c r="C15">
-        <v>294.2864368809746</v>
+        <v>291.8330958761285</v>
       </c>
       <c r="D15">
-        <v>314.6054368809746</v>
+        <v>315.8150958761285</v>
       </c>
       <c r="E15">
-        <v>-95.68100000000001</v>
+        <v>-92.018</v>
       </c>
       <c r="F15">
-        <v>47.619</v>
+        <v>51.282</v>
       </c>
       <c r="G15">
         <v>27.3</v>
@@ -2511,28 +2511,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M15">
-        <v>2.3952357</v>
+        <v>2.5794846</v>
       </c>
       <c r="N15">
-        <v>38.31587541111111</v>
+        <v>38.13162651111111</v>
       </c>
       <c r="O15">
-        <v>9.195810098666666</v>
+        <v>9.151590362666665</v>
       </c>
       <c r="P15">
-        <v>29.12006531244444</v>
+        <v>28.98003614844444</v>
       </c>
       <c r="Q15">
-        <v>39.52006531244444</v>
+        <v>39.38003614844444</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1133308836450222</v>
+        <v>0.1139468875190334</v>
       </c>
       <c r="T15">
-        <v>1.388506045228222</v>
+        <v>1.401171733233203</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.99670354408592</v>
+        <v>15.78265329093692</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1033462432663687</v>
+        <v>0.1031249777615682</v>
       </c>
       <c r="C16">
-        <v>291.8330958761285</v>
+        <v>289.3890930627183</v>
       </c>
       <c r="D16">
-        <v>315.8150958761285</v>
+        <v>317.0340930627183</v>
       </c>
       <c r="E16">
-        <v>-92.018</v>
+        <v>-88.355</v>
       </c>
       <c r="F16">
-        <v>51.282</v>
+        <v>54.94500000000001</v>
       </c>
       <c r="G16">
         <v>27.3</v>
@@ -2593,28 +2593,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M16">
-        <v>2.5794846</v>
+        <v>2.7637335</v>
       </c>
       <c r="N16">
-        <v>38.13162651111111</v>
+        <v>37.94737761111111</v>
       </c>
       <c r="O16">
-        <v>9.151590362666665</v>
+        <v>9.107370626666665</v>
       </c>
       <c r="P16">
-        <v>28.98003614844444</v>
+        <v>28.84000698444444</v>
       </c>
       <c r="Q16">
-        <v>39.38003614844444</v>
+        <v>39.24000698444444</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1139468875190334</v>
+        <v>0.1145773856018449</v>
       </c>
       <c r="T16">
-        <v>1.401171733233203</v>
+        <v>1.414135437426538</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.78265329093692</v>
+        <v>14.73047640487446</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1031249777615682</v>
+        <v>0.1029037122567676</v>
       </c>
       <c r="C17">
-        <v>289.3890930627183</v>
+        <v>286.9545369916365</v>
       </c>
       <c r="D17">
-        <v>317.0340930627183</v>
+        <v>318.2625369916365</v>
       </c>
       <c r="E17">
-        <v>-88.35500000000002</v>
+        <v>-84.69200000000001</v>
       </c>
       <c r="F17">
-        <v>54.945</v>
+        <v>58.608</v>
       </c>
       <c r="G17">
         <v>27.3</v>
@@ -2675,28 +2675,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M17">
-        <v>2.7637335</v>
+        <v>2.9479824</v>
       </c>
       <c r="N17">
-        <v>37.94737761111111</v>
+        <v>37.76312871111111</v>
       </c>
       <c r="O17">
-        <v>9.107370626666665</v>
+        <v>9.063150890666666</v>
       </c>
       <c r="P17">
-        <v>28.84000698444444</v>
+        <v>28.69997782044444</v>
       </c>
       <c r="Q17">
-        <v>39.24000698444444</v>
+        <v>39.09997782044444</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1145773856018449</v>
+        <v>0.1152228955437709</v>
       </c>
       <c r="T17">
-        <v>1.414135437426538</v>
+        <v>1.427407801243523</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.73047640487446</v>
+        <v>13.80982162956981</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1029037122567676</v>
+        <v>0.102682446751967</v>
       </c>
       <c r="C18">
-        <v>286.9545369916365</v>
+        <v>284.5295379027722</v>
       </c>
       <c r="D18">
-        <v>318.2625369916365</v>
+        <v>319.5005379027722</v>
       </c>
       <c r="E18">
-        <v>-84.69200000000001</v>
+        <v>-81.029</v>
       </c>
       <c r="F18">
-        <v>58.608</v>
+        <v>62.27100000000001</v>
       </c>
       <c r="G18">
         <v>27.3</v>
@@ -2757,28 +2757,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M18">
-        <v>2.9479824</v>
+        <v>3.1322313</v>
       </c>
       <c r="N18">
-        <v>37.76312871111111</v>
+        <v>37.57887981111111</v>
       </c>
       <c r="O18">
-        <v>9.063150890666666</v>
+        <v>9.018931154666666</v>
       </c>
       <c r="P18">
-        <v>28.69997782044444</v>
+        <v>28.55994865644444</v>
       </c>
       <c r="Q18">
-        <v>39.09997782044444</v>
+        <v>38.95994865644444</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1152228955437709</v>
+        <v>0.1158839599421289</v>
       </c>
       <c r="T18">
-        <v>1.427407801243523</v>
+        <v>1.440999981056097</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.80982162956981</v>
+        <v>12.99747918077158</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.102682446751967</v>
+        <v>0.1026663812471664</v>
       </c>
       <c r="C19">
-        <v>284.5295379027722</v>
+        <v>280.9568010303511</v>
       </c>
       <c r="D19">
-        <v>319.5005379027722</v>
+        <v>319.5908010303511</v>
       </c>
       <c r="E19">
-        <v>-81.029</v>
+        <v>-77.366</v>
       </c>
       <c r="F19">
-        <v>62.27100000000001</v>
+        <v>65.93400000000001</v>
       </c>
       <c r="G19">
         <v>27.3</v>
@@ -2839,45 +2839,45 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M19">
-        <v>3.1322313</v>
+        <v>3.415381200000001</v>
       </c>
       <c r="N19">
-        <v>37.57887981111111</v>
+        <v>37.29572991111111</v>
       </c>
       <c r="O19">
-        <v>9.018931154666666</v>
+        <v>8.950975178666665</v>
       </c>
       <c r="P19">
-        <v>28.55994865644444</v>
+        <v>28.34475473244444</v>
       </c>
       <c r="Q19">
-        <v>38.95994865644444</v>
+        <v>38.74475473244444</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1158839599421289</v>
+        <v>0.1165611478623981</v>
       </c>
       <c r="T19">
-        <v>1.440999981056097</v>
+        <v>1.454923677449467</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.24</v>
       </c>
       <c r="W19">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>12.99747918077158</v>
+        <v>11.91993183985176</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1026663812471664</v>
+        <v>0.1024565157423658</v>
       </c>
       <c r="C20">
-        <v>280.9568010303511</v>
+        <v>278.4776204712227</v>
       </c>
       <c r="D20">
-        <v>319.5908010303511</v>
+        <v>320.7746204712227</v>
       </c>
       <c r="E20">
-        <v>-77.36600000000001</v>
+        <v>-73.703</v>
       </c>
       <c r="F20">
-        <v>65.934</v>
+        <v>69.59700000000001</v>
       </c>
       <c r="G20">
         <v>27.3</v>
@@ -2921,28 +2921,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M20">
-        <v>3.4153812</v>
+        <v>3.6051246</v>
       </c>
       <c r="N20">
-        <v>37.29572991111111</v>
+        <v>37.10598651111111</v>
       </c>
       <c r="O20">
-        <v>8.950975178666665</v>
+        <v>8.905436762666666</v>
       </c>
       <c r="P20">
-        <v>28.34475473244444</v>
+        <v>28.20054974844444</v>
       </c>
       <c r="Q20">
-        <v>38.74475473244444</v>
+        <v>38.60054974844444</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1165611478623981</v>
+        <v>0.1172550564720566</v>
       </c>
       <c r="T20">
-        <v>1.454923677449467</v>
+        <v>1.469191168815512</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.91993183985176</v>
+        <v>11.29256700617535</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1024565157423658</v>
+        <v>0.1022466502375652</v>
       </c>
       <c r="C21">
-        <v>278.4776204712227</v>
+        <v>276.0072426617174</v>
       </c>
       <c r="D21">
-        <v>320.7746204712227</v>
+        <v>321.9672426617174</v>
       </c>
       <c r="E21">
-        <v>-73.703</v>
+        <v>-70.04000000000001</v>
       </c>
       <c r="F21">
-        <v>69.59700000000001</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="G21">
         <v>27.3</v>
@@ -3003,28 +3003,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M21">
-        <v>3.6051246</v>
+        <v>3.794868</v>
       </c>
       <c r="N21">
-        <v>37.10598651111111</v>
+        <v>36.91624311111111</v>
       </c>
       <c r="O21">
-        <v>8.905436762666666</v>
+        <v>8.859898346666666</v>
       </c>
       <c r="P21">
-        <v>28.20054974844444</v>
+        <v>28.05634476444444</v>
       </c>
       <c r="Q21">
-        <v>38.60054974844444</v>
+        <v>38.45634476444444</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1172550564720566</v>
+        <v>0.1179663127969565</v>
       </c>
       <c r="T21">
-        <v>1.469191168815512</v>
+        <v>1.483815347465708</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.29256700617535</v>
+        <v>10.72793865586658</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1022466502375652</v>
+        <v>0.1020367847327647</v>
       </c>
       <c r="C22">
-        <v>276.0072426617174</v>
+        <v>273.5457661526414</v>
       </c>
       <c r="D22">
-        <v>321.9672426617174</v>
+        <v>323.1687661526414</v>
       </c>
       <c r="E22">
-        <v>-70.04000000000001</v>
+        <v>-66.377</v>
       </c>
       <c r="F22">
-        <v>73.26000000000001</v>
+        <v>76.92300000000002</v>
       </c>
       <c r="G22">
         <v>27.3</v>
@@ -3085,28 +3085,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M22">
-        <v>3.794868</v>
+        <v>3.984611400000001</v>
       </c>
       <c r="N22">
-        <v>36.91624311111111</v>
+        <v>36.72649971111111</v>
       </c>
       <c r="O22">
-        <v>8.859898346666666</v>
+        <v>8.814359930666667</v>
       </c>
       <c r="P22">
-        <v>28.05634476444444</v>
+        <v>27.91213978044444</v>
       </c>
       <c r="Q22">
-        <v>38.45634476444444</v>
+        <v>38.31213978044444</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1179663127969565</v>
+        <v>0.1186955756110945</v>
       </c>
       <c r="T22">
-        <v>1.483815347465708</v>
+        <v>1.498809758486796</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.72793865586658</v>
+        <v>10.21708443415865</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1020367847327647</v>
+        <v>0.1021111592279641</v>
       </c>
       <c r="C23">
-        <v>273.5457661526414</v>
+        <v>269.4559322146378</v>
       </c>
       <c r="D23">
-        <v>323.1687661526414</v>
+        <v>322.7419322146378</v>
       </c>
       <c r="E23">
-        <v>-66.37700000000001</v>
+        <v>-62.71400000000001</v>
       </c>
       <c r="F23">
-        <v>76.923</v>
+        <v>80.586</v>
       </c>
       <c r="G23">
         <v>27.3</v>
@@ -3167,45 +3167,45 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M23">
-        <v>3.9846114</v>
+        <v>4.311351</v>
       </c>
       <c r="N23">
-        <v>36.72649971111111</v>
+        <v>36.39976011111111</v>
       </c>
       <c r="O23">
-        <v>8.814359930666667</v>
+        <v>8.735942426666666</v>
       </c>
       <c r="P23">
-        <v>27.91213978044444</v>
+        <v>27.66381768444444</v>
       </c>
       <c r="Q23">
-        <v>38.31213978044444</v>
+        <v>38.06381768444444</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1186955756110945</v>
+        <v>0.1194435374717488</v>
       </c>
       <c r="T23">
-        <v>1.498809758486796</v>
+        <v>1.514188641585347</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.24</v>
       </c>
       <c r="W23">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>10.21708443415865</v>
+        <v>9.442773532266592</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1021111592279641</v>
+        <v>0.1019142137231635</v>
       </c>
       <c r="C24">
-        <v>269.4559322146378</v>
+        <v>266.9256679074857</v>
       </c>
       <c r="D24">
-        <v>322.7419322146378</v>
+        <v>323.8746679074857</v>
       </c>
       <c r="E24">
-        <v>-62.71400000000001</v>
+        <v>-59.051</v>
       </c>
       <c r="F24">
-        <v>80.586</v>
+        <v>84.24900000000001</v>
       </c>
       <c r="G24">
         <v>27.3</v>
@@ -3249,28 +3249,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M24">
-        <v>4.311351</v>
+        <v>4.507321500000001</v>
       </c>
       <c r="N24">
-        <v>36.39976011111111</v>
+        <v>36.20378961111111</v>
       </c>
       <c r="O24">
-        <v>8.735942426666666</v>
+        <v>8.688909506666665</v>
       </c>
       <c r="P24">
-        <v>27.66381768444444</v>
+        <v>27.51488010444444</v>
       </c>
       <c r="Q24">
-        <v>38.06381768444444</v>
+        <v>37.91488010444444</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1194435374717488</v>
+        <v>0.1202109269131993</v>
       </c>
       <c r="T24">
-        <v>1.514188641585347</v>
+        <v>1.529966976192951</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.442773532266592</v>
+        <v>9.032218161298479</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1019142137231635</v>
+        <v>0.1017172682183629</v>
       </c>
       <c r="C25">
-        <v>266.9256679074857</v>
+        <v>264.4033827885145</v>
       </c>
       <c r="D25">
-        <v>323.8746679074857</v>
+        <v>325.0153827885145</v>
       </c>
       <c r="E25">
-        <v>-59.051</v>
+        <v>-55.38800000000001</v>
       </c>
       <c r="F25">
-        <v>84.24900000000001</v>
+        <v>87.91200000000001</v>
       </c>
       <c r="G25">
         <v>27.3</v>
@@ -3331,28 +3331,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M25">
-        <v>4.507321500000001</v>
+        <v>4.703292</v>
       </c>
       <c r="N25">
-        <v>36.20378961111111</v>
+        <v>36.00781911111111</v>
       </c>
       <c r="O25">
-        <v>8.688909506666665</v>
+        <v>8.641876586666667</v>
       </c>
       <c r="P25">
-        <v>27.51488010444444</v>
+        <v>27.36594252444444</v>
       </c>
       <c r="Q25">
-        <v>37.91488010444444</v>
+        <v>37.76594252444444</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1202109269131993</v>
+        <v>0.1209985108136354</v>
       </c>
       <c r="T25">
-        <v>1.529966976192951</v>
+        <v>1.546160530132335</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.032218161298479</v>
+        <v>8.655875737911044</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1017172682183629</v>
+        <v>0.1015203227135623</v>
       </c>
       <c r="C26">
-        <v>264.4033827885145</v>
+        <v>261.8891614659155</v>
       </c>
       <c r="D26">
-        <v>325.0153827885145</v>
+        <v>326.1641614659155</v>
       </c>
       <c r="E26">
-        <v>-55.38800000000001</v>
+        <v>-51.72500000000001</v>
       </c>
       <c r="F26">
-        <v>87.91200000000001</v>
+        <v>91.575</v>
       </c>
       <c r="G26">
         <v>27.3</v>
@@ -3413,28 +3413,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M26">
-        <v>4.703292</v>
+        <v>4.8992625</v>
       </c>
       <c r="N26">
-        <v>36.00781911111111</v>
+        <v>35.81184861111111</v>
       </c>
       <c r="O26">
-        <v>8.641876586666667</v>
+        <v>8.594843666666666</v>
       </c>
       <c r="P26">
-        <v>27.36594252444444</v>
+        <v>27.21700494444444</v>
       </c>
       <c r="Q26">
-        <v>37.76594252444444</v>
+        <v>37.61700494444445</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1209985108136354</v>
+        <v>0.1218070969514164</v>
       </c>
       <c r="T26">
-        <v>1.546160530132335</v>
+        <v>1.562785912176768</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.655875737911044</v>
+        <v>8.309640708394603</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1015203227135623</v>
+        <v>0.1013233772087617</v>
       </c>
       <c r="C27">
-        <v>261.8891614659155</v>
+        <v>259.3830897483261</v>
       </c>
       <c r="D27">
-        <v>326.1641614659155</v>
+        <v>327.3210897483261</v>
       </c>
       <c r="E27">
-        <v>-51.72500000000001</v>
+        <v>-48.06200000000001</v>
       </c>
       <c r="F27">
-        <v>91.575</v>
+        <v>95.238</v>
       </c>
       <c r="G27">
         <v>27.3</v>
@@ -3495,28 +3495,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M27">
-        <v>4.8992625</v>
+        <v>5.095232999999999</v>
       </c>
       <c r="N27">
-        <v>35.81184861111111</v>
+        <v>35.61587811111111</v>
       </c>
       <c r="O27">
-        <v>8.594843666666666</v>
+        <v>8.547810746666666</v>
       </c>
       <c r="P27">
-        <v>27.21700494444444</v>
+        <v>27.06806736444444</v>
       </c>
       <c r="Q27">
-        <v>37.61700494444445</v>
+        <v>37.46806736444444</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1218070969514164</v>
+        <v>0.1226375367685969</v>
       </c>
       <c r="T27">
-        <v>1.562785912176768</v>
+        <v>1.579860628871051</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.309640708394603</v>
+        <v>7.990039142687118</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1013233772087617</v>
+        <v>0.1011264317039612</v>
       </c>
       <c r="C28">
-        <v>259.3830897483261</v>
+        <v>256.8852546661955</v>
       </c>
       <c r="D28">
-        <v>327.3210897483261</v>
+        <v>328.4862546661955</v>
       </c>
       <c r="E28">
-        <v>-48.06200000000001</v>
+        <v>-44.399</v>
       </c>
       <c r="F28">
-        <v>95.238</v>
+        <v>98.90100000000001</v>
       </c>
       <c r="G28">
         <v>27.3</v>
@@ -3577,28 +3577,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M28">
-        <v>5.095232999999999</v>
+        <v>5.291203500000001</v>
       </c>
       <c r="N28">
-        <v>35.61587811111111</v>
+        <v>35.41990761111111</v>
       </c>
       <c r="O28">
-        <v>8.547810746666666</v>
+        <v>8.500777826666665</v>
       </c>
       <c r="P28">
-        <v>27.06806736444444</v>
+        <v>26.91912978444444</v>
       </c>
       <c r="Q28">
-        <v>37.46806736444444</v>
+        <v>37.31912978444444</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1226375367685969</v>
+        <v>0.1234907283615906</v>
       </c>
       <c r="T28">
-        <v>1.579860628871051</v>
+        <v>1.597403146022712</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.990039142687118</v>
+        <v>7.694111767032037</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1011264317039612</v>
+        <v>0.1010997261991606</v>
       </c>
       <c r="C29">
-        <v>256.8852546661955</v>
+        <v>253.3808882048015</v>
       </c>
       <c r="D29">
-        <v>328.4862546661955</v>
+        <v>328.6448882048015</v>
       </c>
       <c r="E29">
-        <v>-44.399</v>
+        <v>-40.736</v>
       </c>
       <c r="F29">
-        <v>98.90100000000001</v>
+        <v>102.564</v>
       </c>
       <c r="G29">
         <v>27.3</v>
@@ -3659,45 +3659,45 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M29">
-        <v>5.291203500000001</v>
+        <v>5.569225200000001</v>
       </c>
       <c r="N29">
-        <v>35.41990761111111</v>
+        <v>35.14188591111111</v>
       </c>
       <c r="O29">
-        <v>8.500777826666665</v>
+        <v>8.434052618666666</v>
       </c>
       <c r="P29">
-        <v>26.91912978444444</v>
+        <v>26.70783329244444</v>
       </c>
       <c r="Q29">
-        <v>37.31912978444444</v>
+        <v>37.10783329244444</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1234907283615906</v>
+        <v>0.1243676197210563</v>
       </c>
       <c r="T29">
-        <v>1.597403146022712</v>
+        <v>1.615432955317475</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.24</v>
       </c>
       <c r="W29">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.694111767032037</v>
+        <v>7.310013448748868</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1010997261991606</v>
+        <v>0.10090886069436</v>
       </c>
       <c r="C30">
-        <v>253.3808882048015</v>
+        <v>250.8561257168276</v>
       </c>
       <c r="D30">
-        <v>328.6448882048015</v>
+        <v>329.7831257168277</v>
       </c>
       <c r="E30">
-        <v>-40.736</v>
+        <v>-37.07299999999999</v>
       </c>
       <c r="F30">
-        <v>102.564</v>
+        <v>106.227</v>
       </c>
       <c r="G30">
         <v>27.3</v>
@@ -3741,28 +3741,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M30">
-        <v>5.569225200000001</v>
+        <v>5.768126100000001</v>
       </c>
       <c r="N30">
-        <v>35.14188591111111</v>
+        <v>34.94298501111111</v>
       </c>
       <c r="O30">
-        <v>8.434052618666666</v>
+        <v>8.386316402666665</v>
       </c>
       <c r="P30">
-        <v>26.70783329244444</v>
+        <v>26.55666860844444</v>
       </c>
       <c r="Q30">
-        <v>37.10783329244444</v>
+        <v>36.95666860844444</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1243676197210563</v>
+        <v>0.1252692122455774</v>
       </c>
       <c r="T30">
-        <v>1.615432955317475</v>
+        <v>1.633970646564203</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.310013448748868</v>
+        <v>7.057944019481665</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.10090886069436</v>
+        <v>0.1007179951895594</v>
       </c>
       <c r="C31">
-        <v>250.8561257168277</v>
+        <v>248.3392750354142</v>
       </c>
       <c r="D31">
-        <v>329.7831257168277</v>
+        <v>330.9292750354142</v>
       </c>
       <c r="E31">
-        <v>-37.07300000000002</v>
+        <v>-33.41000000000001</v>
       </c>
       <c r="F31">
-        <v>106.227</v>
+        <v>109.89</v>
       </c>
       <c r="G31">
         <v>27.3</v>
@@ -3823,28 +3823,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M31">
-        <v>5.7681261</v>
+        <v>5.967027</v>
       </c>
       <c r="N31">
-        <v>34.94298501111111</v>
+        <v>34.74408411111111</v>
       </c>
       <c r="O31">
-        <v>8.386316402666665</v>
+        <v>8.338580186666665</v>
       </c>
       <c r="P31">
-        <v>26.55666860844444</v>
+        <v>26.40550392444444</v>
       </c>
       <c r="Q31">
-        <v>36.95666860844444</v>
+        <v>36.80550392444444</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1252692122455774</v>
+        <v>0.1261965645565134</v>
       </c>
       <c r="T31">
-        <v>1.633970646564203</v>
+        <v>1.653037986132265</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.057944019481666</v>
+        <v>6.822679218832278</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1007179951895594</v>
+        <v>0.1005271296847588</v>
       </c>
       <c r="C32">
-        <v>248.3392750354142</v>
+        <v>245.83041893985</v>
       </c>
       <c r="D32">
-        <v>330.9292750354142</v>
+        <v>332.08341893985</v>
       </c>
       <c r="E32">
-        <v>-33.41000000000001</v>
+        <v>-29.74700000000001</v>
       </c>
       <c r="F32">
-        <v>109.89</v>
+        <v>113.553</v>
       </c>
       <c r="G32">
         <v>27.3</v>
@@ -3905,28 +3905,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M32">
-        <v>5.967027</v>
+        <v>6.1659279</v>
       </c>
       <c r="N32">
-        <v>34.74408411111111</v>
+        <v>34.54518321111111</v>
       </c>
       <c r="O32">
-        <v>8.338580186666665</v>
+        <v>8.290843970666666</v>
       </c>
       <c r="P32">
-        <v>26.40550392444444</v>
+        <v>26.25433924044444</v>
       </c>
       <c r="Q32">
-        <v>36.80550392444444</v>
+        <v>36.65433924044444</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1261965645565134</v>
+        <v>0.127150796644578</v>
       </c>
       <c r="T32">
-        <v>1.653037986132265</v>
+        <v>1.672658002209548</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.822679218832278</v>
+        <v>6.602592792418333</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1005271296847588</v>
+        <v>0.1003362641799582</v>
       </c>
       <c r="C33">
-        <v>245.83041893985</v>
+        <v>243.329641368264</v>
       </c>
       <c r="D33">
-        <v>332.08341893985</v>
+        <v>333.245641368264</v>
       </c>
       <c r="E33">
-        <v>-29.74700000000001</v>
+        <v>-26.084</v>
       </c>
       <c r="F33">
-        <v>113.553</v>
+        <v>117.216</v>
       </c>
       <c r="G33">
         <v>27.3</v>
@@ -3987,28 +3987,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M33">
-        <v>6.1659279</v>
+        <v>6.364828800000001</v>
       </c>
       <c r="N33">
-        <v>34.54518321111111</v>
+        <v>34.34628231111111</v>
       </c>
       <c r="O33">
-        <v>8.290843970666666</v>
+        <v>8.243107754666667</v>
       </c>
       <c r="P33">
-        <v>26.25433924044444</v>
+        <v>26.10317455644444</v>
       </c>
       <c r="Q33">
-        <v>36.65433924044444</v>
+        <v>36.50317455644444</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.127150796644578</v>
+        <v>0.1281330943822915</v>
       </c>
       <c r="T33">
-        <v>1.672658002209548</v>
+        <v>1.69285507758322</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.602592792418333</v>
+        <v>6.39626176765526</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1003362641799582</v>
+        <v>0.1001453986751576</v>
       </c>
       <c r="C34">
-        <v>243.329641368264</v>
+        <v>240.837027437976</v>
       </c>
       <c r="D34">
-        <v>333.245641368264</v>
+        <v>334.416027437976</v>
       </c>
       <c r="E34">
-        <v>-26.084</v>
+        <v>-22.42100000000001</v>
       </c>
       <c r="F34">
-        <v>117.216</v>
+        <v>120.879</v>
       </c>
       <c r="G34">
         <v>27.3</v>
@@ -4069,28 +4069,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M34">
-        <v>6.364828800000001</v>
+        <v>6.563729700000001</v>
       </c>
       <c r="N34">
-        <v>34.34628231111111</v>
+        <v>34.14738141111111</v>
       </c>
       <c r="O34">
-        <v>8.243107754666667</v>
+        <v>8.195371538666665</v>
       </c>
       <c r="P34">
-        <v>26.10317455644444</v>
+        <v>25.95200987244444</v>
       </c>
       <c r="Q34">
-        <v>36.50317455644444</v>
+        <v>36.35200987244444</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1281330943822915</v>
+        <v>0.1291447144405338</v>
       </c>
       <c r="T34">
-        <v>1.69285507758322</v>
+        <v>1.713655050729241</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.39626176765526</v>
+        <v>6.202435653483888</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1001453986751576</v>
+        <v>0.1002129331703571</v>
       </c>
       <c r="C35">
-        <v>240.837027437976</v>
+        <v>236.7589677033921</v>
       </c>
       <c r="D35">
-        <v>334.416027437976</v>
+        <v>334.0009677033921</v>
       </c>
       <c r="E35">
-        <v>-22.42100000000001</v>
+        <v>-18.758</v>
       </c>
       <c r="F35">
-        <v>120.879</v>
+        <v>124.542</v>
       </c>
       <c r="G35">
         <v>27.3</v>
@@ -4151,45 +4151,45 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M35">
-        <v>6.563729700000001</v>
+        <v>6.887172600000001</v>
       </c>
       <c r="N35">
-        <v>34.14738141111111</v>
+        <v>33.82393851111111</v>
       </c>
       <c r="O35">
-        <v>8.195371538666665</v>
+        <v>8.117745242666667</v>
       </c>
       <c r="P35">
-        <v>25.95200987244444</v>
+        <v>25.70619326844444</v>
       </c>
       <c r="Q35">
-        <v>36.35200987244444</v>
+        <v>36.10619326844444</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1291447144405338</v>
+        <v>0.1301869896520562</v>
       </c>
       <c r="T35">
-        <v>1.713655050729241</v>
+        <v>1.735085326091809</v>
       </c>
       <c r="U35">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.24</v>
       </c>
       <c r="W35">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>6.202435653483888</v>
+        <v>5.911150115667365</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1002129331703571</v>
+        <v>0.1000296676655565</v>
       </c>
       <c r="C36">
-        <v>236.7589677033921</v>
+        <v>234.2247014497896</v>
       </c>
       <c r="D36">
-        <v>334.0009677033921</v>
+        <v>335.1297014497896</v>
       </c>
       <c r="E36">
-        <v>-18.758</v>
+        <v>-15.095</v>
       </c>
       <c r="F36">
-        <v>124.542</v>
+        <v>128.205</v>
       </c>
       <c r="G36">
         <v>27.3</v>
@@ -4233,28 +4233,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M36">
-        <v>6.887172600000001</v>
+        <v>7.089736500000001</v>
       </c>
       <c r="N36">
-        <v>33.82393851111111</v>
+        <v>33.62137461111111</v>
       </c>
       <c r="O36">
-        <v>8.117745242666667</v>
+        <v>8.069129906666666</v>
       </c>
       <c r="P36">
-        <v>25.70619326844444</v>
+        <v>25.55224470444444</v>
       </c>
       <c r="Q36">
-        <v>36.10619326844444</v>
+        <v>35.95224470444444</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1301869896520562</v>
+        <v>0.1312613348700869</v>
       </c>
       <c r="T36">
-        <v>1.735085326091809</v>
+        <v>1.757174994542455</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.911150115667365</v>
+        <v>5.742260112362583</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1000296676655565</v>
+        <v>0.0998464021607559</v>
       </c>
       <c r="C37">
-        <v>234.2247014497896</v>
+        <v>231.6980900243184</v>
       </c>
       <c r="D37">
-        <v>335.1297014497896</v>
+        <v>336.2660900243184</v>
       </c>
       <c r="E37">
-        <v>-15.095</v>
+        <v>-11.43199999999999</v>
       </c>
       <c r="F37">
-        <v>128.205</v>
+        <v>131.868</v>
       </c>
       <c r="G37">
         <v>27.3</v>
@@ -4315,28 +4315,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M37">
-        <v>7.089736500000001</v>
+        <v>7.292300400000001</v>
       </c>
       <c r="N37">
-        <v>33.62137461111111</v>
+        <v>33.41881071111111</v>
       </c>
       <c r="O37">
-        <v>8.069129906666666</v>
+        <v>8.020514570666665</v>
       </c>
       <c r="P37">
-        <v>25.55224470444444</v>
+        <v>25.39829614044444</v>
       </c>
       <c r="Q37">
-        <v>35.95224470444444</v>
+        <v>35.79829614044444</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1312613348700869</v>
+        <v>0.1323692533761811</v>
       </c>
       <c r="T37">
-        <v>1.757174994542455</v>
+        <v>1.779954965132184</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.742260112362583</v>
+        <v>5.582752887019177</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0998464021607559</v>
+        <v>0.09966313665595529</v>
       </c>
       <c r="C38">
-        <v>231.6980900243184</v>
+        <v>229.1792115620087</v>
       </c>
       <c r="D38">
-        <v>336.2660900243184</v>
+        <v>337.4102115620087</v>
       </c>
       <c r="E38">
-        <v>-11.43200000000002</v>
+        <v>-7.769000000000005</v>
       </c>
       <c r="F38">
-        <v>131.868</v>
+        <v>135.531</v>
       </c>
       <c r="G38">
         <v>27.3</v>
@@ -4397,28 +4397,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M38">
-        <v>7.2923004</v>
+        <v>7.494864300000001</v>
       </c>
       <c r="N38">
-        <v>33.41881071111111</v>
+        <v>33.21624681111111</v>
       </c>
       <c r="O38">
-        <v>8.020514570666665</v>
+        <v>7.971899234666665</v>
       </c>
       <c r="P38">
-        <v>25.39829614044444</v>
+        <v>25.24434757644444</v>
       </c>
       <c r="Q38">
-        <v>35.79829614044444</v>
+        <v>35.64434757644444</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1323692533761811</v>
+        <v>0.1335123438983417</v>
       </c>
       <c r="T38">
-        <v>1.779954965132184</v>
+        <v>1.803458109391428</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.582752887019178</v>
+        <v>5.431867673856497</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09966313665595529</v>
+        <v>0.09947987115115473</v>
       </c>
       <c r="C39">
-        <v>229.1792115620087</v>
+        <v>226.6681452649167</v>
       </c>
       <c r="D39">
-        <v>337.4102115620087</v>
+        <v>338.5621452649167</v>
       </c>
       <c r="E39">
-        <v>-7.769000000000005</v>
+        <v>-4.105999999999995</v>
       </c>
       <c r="F39">
-        <v>135.531</v>
+        <v>139.194</v>
       </c>
       <c r="G39">
         <v>27.3</v>
@@ -4479,28 +4479,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M39">
-        <v>7.494864300000001</v>
+        <v>7.697428200000001</v>
       </c>
       <c r="N39">
-        <v>33.21624681111111</v>
+        <v>33.0136829111111</v>
       </c>
       <c r="O39">
-        <v>7.971899234666665</v>
+        <v>7.923283898666664</v>
       </c>
       <c r="P39">
-        <v>25.24434757644444</v>
+        <v>25.09039901244444</v>
       </c>
       <c r="Q39">
-        <v>35.64434757644444</v>
+        <v>35.49039901244444</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1335123438983417</v>
+        <v>0.1346923083083141</v>
       </c>
       <c r="T39">
-        <v>1.803458109391428</v>
+        <v>1.827719419594518</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.431867673856497</v>
+        <v>5.288923787702378</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09947987115115473</v>
+        <v>0.09929660564635413</v>
       </c>
       <c r="C40">
-        <v>226.6681452649167</v>
+        <v>224.1649714204025</v>
       </c>
       <c r="D40">
-        <v>338.5621452649167</v>
+        <v>339.7219714204024</v>
       </c>
       <c r="E40">
-        <v>-4.105999999999995</v>
+        <v>-0.4430000000000121</v>
       </c>
       <c r="F40">
-        <v>139.194</v>
+        <v>142.857</v>
       </c>
       <c r="G40">
         <v>27.3</v>
@@ -4561,28 +4561,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M40">
-        <v>7.697428200000001</v>
+        <v>7.8999921</v>
       </c>
       <c r="N40">
-        <v>33.0136829111111</v>
+        <v>32.81111901111111</v>
       </c>
       <c r="O40">
-        <v>7.923283898666664</v>
+        <v>7.874668562666666</v>
       </c>
       <c r="P40">
-        <v>25.09039901244444</v>
+        <v>24.93645044844444</v>
       </c>
       <c r="Q40">
-        <v>35.49039901244444</v>
+        <v>35.33645044844444</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1346923083083141</v>
+        <v>0.1359109600759904</v>
       </c>
       <c r="T40">
-        <v>1.827719419594518</v>
+        <v>1.852776182591153</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.288923787702378</v>
+        <v>5.153310357248472</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09929660564635413</v>
+        <v>0.09911334014155355</v>
       </c>
       <c r="C41">
-        <v>224.1649714204025</v>
+        <v>221.6697714197815</v>
       </c>
       <c r="D41">
-        <v>339.7219714204024</v>
+        <v>340.8897714197815</v>
       </c>
       <c r="E41">
-        <v>-0.4430000000000121</v>
+        <v>3.219999999999999</v>
       </c>
       <c r="F41">
-        <v>142.857</v>
+        <v>146.52</v>
       </c>
       <c r="G41">
         <v>27.3</v>
@@ -4643,28 +4643,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M41">
-        <v>7.8999921</v>
+        <v>8.102556000000002</v>
       </c>
       <c r="N41">
-        <v>32.81111901111111</v>
+        <v>32.60855511111111</v>
       </c>
       <c r="O41">
-        <v>7.874668562666666</v>
+        <v>7.826053226666666</v>
       </c>
       <c r="P41">
-        <v>24.93645044844444</v>
+        <v>24.78250188444444</v>
       </c>
       <c r="Q41">
-        <v>35.33645044844444</v>
+        <v>35.18250188444444</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1359109600759904</v>
+        <v>0.1371702335692559</v>
       </c>
       <c r="T41">
-        <v>1.852776182591153</v>
+        <v>1.878668171021009</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.153310357248472</v>
+        <v>5.02447759831726</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09911334014155355</v>
+        <v>0.09893007463675296</v>
       </c>
       <c r="C42">
-        <v>221.6697714197815</v>
+        <v>219.1826277773668</v>
       </c>
       <c r="D42">
-        <v>340.8897714197815</v>
+        <v>342.0656277773668</v>
       </c>
       <c r="E42">
-        <v>3.219999999999999</v>
+        <v>6.88300000000001</v>
       </c>
       <c r="F42">
-        <v>146.52</v>
+        <v>150.183</v>
       </c>
       <c r="G42">
         <v>27.3</v>
@@ -4725,28 +4725,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M42">
-        <v>8.102556000000002</v>
+        <v>8.305119900000001</v>
       </c>
       <c r="N42">
-        <v>32.60855511111111</v>
+        <v>32.40599121111111</v>
       </c>
       <c r="O42">
-        <v>7.826053226666666</v>
+        <v>7.777437890666666</v>
       </c>
       <c r="P42">
-        <v>24.78250188444444</v>
+        <v>24.62855332044444</v>
       </c>
       <c r="Q42">
-        <v>35.18250188444444</v>
+        <v>35.02855332044444</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1371702335692559</v>
+        <v>0.1384721942995813</v>
       </c>
       <c r="T42">
-        <v>1.878668171021009</v>
+        <v>1.90543785397391</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.02447759831726</v>
+        <v>4.901929364211961</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09893007463675296</v>
+        <v>0.09874680913195238</v>
       </c>
       <c r="C43">
-        <v>219.1826277773668</v>
+        <v>216.703624149902</v>
       </c>
       <c r="D43">
-        <v>342.0656277773668</v>
+        <v>343.249624149902</v>
       </c>
       <c r="E43">
-        <v>6.88300000000001</v>
+        <v>10.54600000000002</v>
       </c>
       <c r="F43">
-        <v>150.183</v>
+        <v>153.846</v>
       </c>
       <c r="G43">
         <v>27.3</v>
@@ -4807,28 +4807,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M43">
-        <v>8.305119900000001</v>
+        <v>8.507683800000002</v>
       </c>
       <c r="N43">
-        <v>32.40599121111111</v>
+        <v>32.20342731111111</v>
       </c>
       <c r="O43">
-        <v>7.777437890666666</v>
+        <v>7.728822554666666</v>
       </c>
       <c r="P43">
-        <v>24.62855332044444</v>
+        <v>24.47460475644444</v>
       </c>
       <c r="Q43">
-        <v>35.02855332044444</v>
+        <v>34.87460475644444</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1384721942995813</v>
+        <v>0.1398190502275041</v>
       </c>
       <c r="T43">
-        <v>1.90543785397391</v>
+        <v>1.93313062944243</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.901929364211961</v>
+        <v>4.785216760302152</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09874680913195238</v>
+        <v>0.09856354362715181</v>
       </c>
       <c r="C44">
-        <v>216.7036241499021</v>
+        <v>214.2328453564032</v>
       </c>
       <c r="D44">
-        <v>343.249624149902</v>
+        <v>344.4418453564032</v>
       </c>
       <c r="E44">
-        <v>10.54599999999999</v>
+        <v>14.209</v>
       </c>
       <c r="F44">
-        <v>153.846</v>
+        <v>157.509</v>
       </c>
       <c r="G44">
         <v>27.3</v>
@@ -4889,28 +4889,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M44">
-        <v>8.507683800000001</v>
+        <v>8.710247700000002</v>
       </c>
       <c r="N44">
-        <v>32.20342731111111</v>
+        <v>32.0008634111111</v>
       </c>
       <c r="O44">
-        <v>7.728822554666666</v>
+        <v>7.680207218666665</v>
       </c>
       <c r="P44">
-        <v>24.47460475644444</v>
+        <v>24.32065619244444</v>
       </c>
       <c r="Q44">
-        <v>34.87460475644444</v>
+        <v>34.72065619244444</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1398190502275041</v>
+        <v>0.1412131642581611</v>
       </c>
       <c r="T44">
-        <v>1.93313062944243</v>
+        <v>1.961795081243177</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.785216760302152</v>
+        <v>4.67393264959745</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09856354362715181</v>
+        <v>0.09838027812235121</v>
       </c>
       <c r="C45">
-        <v>214.2328453564032</v>
+        <v>211.7703773984134</v>
       </c>
       <c r="D45">
-        <v>344.4418453564032</v>
+        <v>345.6423773984134</v>
       </c>
       <c r="E45">
-        <v>14.209</v>
+        <v>17.87199999999999</v>
       </c>
       <c r="F45">
-        <v>157.509</v>
+        <v>161.172</v>
       </c>
       <c r="G45">
         <v>27.3</v>
@@ -4971,28 +4971,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M45">
-        <v>8.710247700000002</v>
+        <v>8.9128116</v>
       </c>
       <c r="N45">
-        <v>32.0008634111111</v>
+        <v>31.79829951111111</v>
       </c>
       <c r="O45">
-        <v>7.680207218666665</v>
+        <v>7.631591882666666</v>
       </c>
       <c r="P45">
-        <v>24.32065619244444</v>
+        <v>24.16670762844445</v>
       </c>
       <c r="Q45">
-        <v>34.72065619244444</v>
+        <v>34.56670762844445</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1412131642581611</v>
+        <v>0.1426570680756271</v>
       </c>
       <c r="T45">
-        <v>1.961795081243177</v>
+        <v>1.99148326346538</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.67393264959745</v>
+        <v>4.567706907561147</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09838027812235121</v>
+        <v>0.09905201261755063</v>
       </c>
       <c r="C46">
-        <v>211.7703773984134</v>
+        <v>203.7473561243118</v>
       </c>
       <c r="D46">
-        <v>345.6423773984134</v>
+        <v>341.2823561243118</v>
       </c>
       <c r="E46">
-        <v>17.87199999999999</v>
+        <v>21.535</v>
       </c>
       <c r="F46">
-        <v>161.172</v>
+        <v>164.835</v>
       </c>
       <c r="G46">
         <v>27.3</v>
@@ -5053,45 +5053,45 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M46">
-        <v>8.9128116</v>
+        <v>9.527463000000001</v>
       </c>
       <c r="N46">
-        <v>31.79829951111111</v>
+        <v>31.18364811111111</v>
       </c>
       <c r="O46">
-        <v>7.631591882666666</v>
+        <v>7.484075546666666</v>
       </c>
       <c r="P46">
-        <v>24.16670762844445</v>
+        <v>23.69957256444444</v>
       </c>
       <c r="Q46">
-        <v>34.56670762844445</v>
+        <v>34.09957256444444</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1426570680756271</v>
+        <v>0.1441534774864557</v>
       </c>
       <c r="T46">
-        <v>1.99148326346538</v>
+        <v>2.022251015950209</v>
       </c>
       <c r="U46">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.24</v>
       </c>
       <c r="W46">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.567706907561147</v>
+        <v>4.273027469234056</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09905201261755063</v>
+        <v>0.09888774711275004</v>
       </c>
       <c r="C47">
-        <v>203.7473561243118</v>
+        <v>201.1403609758499</v>
       </c>
       <c r="D47">
-        <v>341.2823561243118</v>
+        <v>342.3383609758499</v>
       </c>
       <c r="E47">
-        <v>21.535</v>
+        <v>25.19800000000001</v>
       </c>
       <c r="F47">
-        <v>164.835</v>
+        <v>168.498</v>
       </c>
       <c r="G47">
         <v>27.3</v>
@@ -5135,28 +5135,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M47">
-        <v>9.527463000000001</v>
+        <v>9.739184400000001</v>
       </c>
       <c r="N47">
-        <v>31.18364811111111</v>
+        <v>30.97192671111111</v>
       </c>
       <c r="O47">
-        <v>7.484075546666666</v>
+        <v>7.433262410666666</v>
       </c>
       <c r="P47">
-        <v>23.69957256444444</v>
+        <v>23.53866430044445</v>
       </c>
       <c r="Q47">
-        <v>34.09957256444444</v>
+        <v>33.93866430044444</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1441534774864557</v>
+        <v>0.1457053094680556</v>
       </c>
       <c r="T47">
-        <v>2.022251015950209</v>
+        <v>2.054158314823364</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.273027469234056</v>
+        <v>4.180135567728968</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09888774711275004</v>
+        <v>0.09872348160794947</v>
       </c>
       <c r="C48">
-        <v>201.1403609758499</v>
+        <v>198.5399211470584</v>
       </c>
       <c r="D48">
-        <v>342.3383609758499</v>
+        <v>343.4009211470585</v>
       </c>
       <c r="E48">
-        <v>25.19800000000001</v>
+        <v>28.86100000000002</v>
       </c>
       <c r="F48">
-        <v>168.498</v>
+        <v>172.161</v>
       </c>
       <c r="G48">
         <v>27.3</v>
@@ -5217,28 +5217,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M48">
-        <v>9.739184400000001</v>
+        <v>9.950905800000003</v>
       </c>
       <c r="N48">
-        <v>30.97192671111111</v>
+        <v>30.76020531111111</v>
       </c>
       <c r="O48">
-        <v>7.433262410666666</v>
+        <v>7.382449274666666</v>
       </c>
       <c r="P48">
-        <v>23.53866430044445</v>
+        <v>23.37775603644444</v>
       </c>
       <c r="Q48">
-        <v>33.93866430044444</v>
+        <v>33.77775603644444</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1457053094680556</v>
+        <v>0.1473157011470745</v>
       </c>
       <c r="T48">
-        <v>2.054158314823364</v>
+        <v>2.087269662710602</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.180135567728968</v>
+        <v>4.091196513096436</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09872348160794947</v>
+        <v>0.09855921610314888</v>
       </c>
       <c r="C49">
-        <v>198.5399211470584</v>
+        <v>195.9460978677839</v>
       </c>
       <c r="D49">
-        <v>343.4009211470585</v>
+        <v>344.4700978677839</v>
       </c>
       <c r="E49">
-        <v>28.86100000000002</v>
+        <v>32.524</v>
       </c>
       <c r="F49">
-        <v>172.161</v>
+        <v>175.824</v>
       </c>
       <c r="G49">
         <v>27.3</v>
@@ -5299,28 +5299,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M49">
-        <v>9.950905800000003</v>
+        <v>10.1626272</v>
       </c>
       <c r="N49">
-        <v>30.76020531111111</v>
+        <v>30.54848391111111</v>
       </c>
       <c r="O49">
-        <v>7.382449274666666</v>
+        <v>7.331636138666665</v>
       </c>
       <c r="P49">
-        <v>23.37775603644444</v>
+        <v>23.21684777244444</v>
       </c>
       <c r="Q49">
-        <v>33.77775603644444</v>
+        <v>33.61684777244444</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1473157011470745</v>
+        <v>0.148988030967594</v>
       </c>
       <c r="T49">
-        <v>2.087269662710602</v>
+        <v>2.121654523978117</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.091196513096436</v>
+        <v>4.005963252406927</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09855921610314888</v>
+        <v>0.09969835059834828</v>
       </c>
       <c r="C50">
-        <v>195.9460978677839</v>
+        <v>185.0027680118657</v>
       </c>
       <c r="D50">
-        <v>344.4700978677839</v>
+        <v>337.1897680118657</v>
       </c>
       <c r="E50">
-        <v>32.524</v>
+        <v>36.18699999999998</v>
       </c>
       <c r="F50">
-        <v>175.824</v>
+        <v>179.487</v>
       </c>
       <c r="G50">
         <v>27.3</v>
@@ -5381,45 +5381,45 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M50">
-        <v>10.1626272</v>
+        <v>11.0025531</v>
       </c>
       <c r="N50">
-        <v>30.54848391111111</v>
+        <v>29.70855801111111</v>
       </c>
       <c r="O50">
-        <v>7.331636138666665</v>
+        <v>7.130053922666666</v>
       </c>
       <c r="P50">
-        <v>23.21684777244444</v>
+        <v>22.57850408844444</v>
       </c>
       <c r="Q50">
-        <v>33.61684777244444</v>
+        <v>32.97850408844444</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.148988030967594</v>
+        <v>0.1507259423497025</v>
       </c>
       <c r="T50">
-        <v>2.121654523978117</v>
+        <v>2.157387811177691</v>
       </c>
       <c r="U50">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V50">
         <v>0.24</v>
       </c>
       <c r="W50">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.005963252406927</v>
+        <v>3.700151295894324</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09969835059834828</v>
+        <v>0.09956068509354769</v>
       </c>
       <c r="C51">
-        <v>185.0027680118657</v>
+        <v>182.2032131027564</v>
       </c>
       <c r="D51">
-        <v>337.1897680118657</v>
+        <v>338.0532131027564</v>
       </c>
       <c r="E51">
-        <v>36.18699999999998</v>
+        <v>39.84999999999999</v>
       </c>
       <c r="F51">
-        <v>179.487</v>
+        <v>183.15</v>
       </c>
       <c r="G51">
         <v>27.3</v>
@@ -5463,28 +5463,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M51">
-        <v>11.0025531</v>
+        <v>11.227095</v>
       </c>
       <c r="N51">
-        <v>29.70855801111111</v>
+        <v>29.48401611111111</v>
       </c>
       <c r="O51">
-        <v>7.130053922666666</v>
+        <v>7.076163866666666</v>
       </c>
       <c r="P51">
-        <v>22.57850408844444</v>
+        <v>22.40785224444445</v>
       </c>
       <c r="Q51">
-        <v>32.97850408844444</v>
+        <v>32.80785224444445</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1507259423497025</v>
+        <v>0.1525333701870954</v>
       </c>
       <c r="T51">
-        <v>2.157387811177691</v>
+        <v>2.194550429865249</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.700151295894324</v>
+        <v>3.626148269976437</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09956068509354769</v>
+        <v>0.09942301958874712</v>
       </c>
       <c r="C52">
-        <v>182.2032131027564</v>
+        <v>179.4080916106838</v>
       </c>
       <c r="D52">
-        <v>338.0532131027564</v>
+        <v>338.9210916106838</v>
       </c>
       <c r="E52">
-        <v>39.84999999999999</v>
+        <v>43.51300000000001</v>
       </c>
       <c r="F52">
-        <v>183.15</v>
+        <v>186.813</v>
       </c>
       <c r="G52">
         <v>27.3</v>
@@ -5545,28 +5545,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M52">
-        <v>11.227095</v>
+        <v>11.4516369</v>
       </c>
       <c r="N52">
-        <v>29.48401611111111</v>
+        <v>29.25947421111111</v>
       </c>
       <c r="O52">
-        <v>7.076163866666666</v>
+        <v>7.022273810666666</v>
       </c>
       <c r="P52">
-        <v>22.40785224444445</v>
+        <v>22.23720040044444</v>
       </c>
       <c r="Q52">
-        <v>32.80785224444445</v>
+        <v>32.63720040044444</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1525333701870954</v>
+        <v>0.1544145705892798</v>
       </c>
       <c r="T52">
-        <v>2.194550429865249</v>
+        <v>2.233229890131891</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.626148269976437</v>
+        <v>3.555047323506311</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09942301958874712</v>
+        <v>0.1003919140839465</v>
       </c>
       <c r="C53">
-        <v>179.4080916106838</v>
+        <v>169.7299374348545</v>
       </c>
       <c r="D53">
-        <v>338.9210916106838</v>
+        <v>332.9059374348545</v>
       </c>
       <c r="E53">
-        <v>43.51300000000001</v>
+        <v>47.17599999999999</v>
       </c>
       <c r="F53">
-        <v>186.813</v>
+        <v>190.476</v>
       </c>
       <c r="G53">
         <v>27.3</v>
@@ -5627,45 +5627,45 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M53">
-        <v>11.4516369</v>
+        <v>12.2095116</v>
       </c>
       <c r="N53">
-        <v>29.25947421111111</v>
+        <v>28.50159951111111</v>
       </c>
       <c r="O53">
-        <v>7.022273810666666</v>
+        <v>6.840383882666666</v>
       </c>
       <c r="P53">
-        <v>22.23720040044444</v>
+        <v>21.66121562844445</v>
       </c>
       <c r="Q53">
-        <v>32.63720040044444</v>
+        <v>32.06121562844444</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1544145705892798</v>
+        <v>0.1563741543415553</v>
       </c>
       <c r="T53">
-        <v>2.233229890131891</v>
+        <v>2.273520994576309</v>
       </c>
       <c r="U53">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V53">
         <v>0.24</v>
       </c>
       <c r="W53">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.555047323506311</v>
+        <v>3.334376709311706</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1003919140839465</v>
+        <v>0.100275528579146</v>
       </c>
       <c r="C54">
-        <v>169.7299374348545</v>
+        <v>166.778182035688</v>
       </c>
       <c r="D54">
-        <v>332.9059374348545</v>
+        <v>333.617182035688</v>
       </c>
       <c r="E54">
-        <v>47.17599999999999</v>
+        <v>50.839</v>
       </c>
       <c r="F54">
-        <v>190.476</v>
+        <v>194.139</v>
       </c>
       <c r="G54">
         <v>27.3</v>
@@ -5709,28 +5709,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M54">
-        <v>12.2095116</v>
+        <v>12.4443099</v>
       </c>
       <c r="N54">
-        <v>28.50159951111111</v>
+        <v>28.26680121111111</v>
       </c>
       <c r="O54">
-        <v>6.840383882666666</v>
+        <v>6.784032290666666</v>
       </c>
       <c r="P54">
-        <v>21.66121562844445</v>
+        <v>21.48276892044444</v>
       </c>
       <c r="Q54">
-        <v>32.06121562844444</v>
+        <v>31.88276892044444</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1563741543415553</v>
+        <v>0.1584171246364807</v>
       </c>
       <c r="T54">
-        <v>2.273520994576309</v>
+        <v>2.315526614103469</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.334376709311706</v>
+        <v>3.271463941211485</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.100275528579146</v>
+        <v>0.1001591430743454</v>
       </c>
       <c r="C55">
-        <v>166.778182035688</v>
+        <v>163.829472253403</v>
       </c>
       <c r="D55">
-        <v>333.617182035688</v>
+        <v>334.331472253403</v>
       </c>
       <c r="E55">
-        <v>50.839</v>
+        <v>54.50200000000001</v>
       </c>
       <c r="F55">
-        <v>194.139</v>
+        <v>197.802</v>
       </c>
       <c r="G55">
         <v>27.3</v>
@@ -5791,28 +5791,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M55">
-        <v>12.4443099</v>
+        <v>12.6791082</v>
       </c>
       <c r="N55">
-        <v>28.26680121111111</v>
+        <v>28.03200291111111</v>
       </c>
       <c r="O55">
-        <v>6.784032290666666</v>
+        <v>6.727680698666665</v>
       </c>
       <c r="P55">
-        <v>21.48276892044444</v>
+        <v>21.30432221244444</v>
       </c>
       <c r="Q55">
-        <v>31.88276892044444</v>
+        <v>31.70432221244444</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1584171246364807</v>
+        <v>0.1605489197268377</v>
       </c>
       <c r="T55">
-        <v>2.315526614103469</v>
+        <v>2.359358564914418</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.271463941211485</v>
+        <v>3.210881275633495</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1001591430743454</v>
+        <v>0.1000427575695448</v>
       </c>
       <c r="C56">
-        <v>163.829472253403</v>
+        <v>160.8838276924041</v>
       </c>
       <c r="D56">
-        <v>334.331472253403</v>
+        <v>335.0488276924041</v>
       </c>
       <c r="E56">
-        <v>54.50200000000001</v>
+        <v>58.16500000000002</v>
       </c>
       <c r="F56">
-        <v>197.802</v>
+        <v>201.465</v>
       </c>
       <c r="G56">
         <v>27.3</v>
@@ -5873,28 +5873,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M56">
-        <v>12.6791082</v>
+        <v>12.9139065</v>
       </c>
       <c r="N56">
-        <v>28.03200291111111</v>
+        <v>27.79720461111111</v>
       </c>
       <c r="O56">
-        <v>6.727680698666665</v>
+        <v>6.671329106666665</v>
       </c>
       <c r="P56">
-        <v>21.30432221244444</v>
+        <v>21.12587550444444</v>
       </c>
       <c r="Q56">
-        <v>31.70432221244444</v>
+        <v>31.52587550444444</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1605489197268377</v>
+        <v>0.1627754612656551</v>
       </c>
       <c r="T56">
-        <v>2.359358564914418</v>
+        <v>2.405138602428076</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.210881275633495</v>
+        <v>3.152501616076522</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1000427575695448</v>
+        <v>0.0999263720647442</v>
       </c>
       <c r="C57">
-        <v>160.8838276924041</v>
+        <v>157.9412681257142</v>
       </c>
       <c r="D57">
-        <v>335.0488276924041</v>
+        <v>335.7692681257142</v>
       </c>
       <c r="E57">
-        <v>58.16500000000002</v>
+        <v>61.828</v>
       </c>
       <c r="F57">
-        <v>201.465</v>
+        <v>205.128</v>
       </c>
       <c r="G57">
         <v>27.3</v>
@@ -5955,28 +5955,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M57">
-        <v>12.9139065</v>
+        <v>13.1487048</v>
       </c>
       <c r="N57">
-        <v>27.79720461111111</v>
+        <v>27.5624063111111</v>
       </c>
       <c r="O57">
-        <v>6.671329106666665</v>
+        <v>6.614977514666665</v>
       </c>
       <c r="P57">
-        <v>21.12587550444444</v>
+        <v>20.94742879644444</v>
       </c>
       <c r="Q57">
-        <v>31.52587550444444</v>
+        <v>31.34742879644444</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1627754612656551</v>
+        <v>0.165103209238055</v>
       </c>
       <c r="T57">
-        <v>2.405138602428076</v>
+        <v>2.45299955073781</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.152501616076522</v>
+        <v>3.09620694436087</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0999263720647442</v>
+        <v>0.09980998655994361</v>
       </c>
       <c r="C58">
-        <v>157.9412681257142</v>
+        <v>155.0018134967903</v>
       </c>
       <c r="D58">
-        <v>335.7692681257142</v>
+        <v>336.4928134967903</v>
       </c>
       <c r="E58">
-        <v>61.828</v>
+        <v>65.49100000000001</v>
       </c>
       <c r="F58">
-        <v>205.128</v>
+        <v>208.791</v>
       </c>
       <c r="G58">
         <v>27.3</v>
@@ -6037,28 +6037,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M58">
-        <v>13.1487048</v>
+        <v>13.3835031</v>
       </c>
       <c r="N58">
-        <v>27.5624063111111</v>
+        <v>27.32760801111111</v>
       </c>
       <c r="O58">
-        <v>6.614977514666665</v>
+        <v>6.558625922666665</v>
       </c>
       <c r="P58">
-        <v>20.94742879644444</v>
+        <v>20.76898208844444</v>
       </c>
       <c r="Q58">
-        <v>31.34742879644444</v>
+        <v>31.16898208844444</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.165103209238055</v>
+        <v>0.1675392245580084</v>
       </c>
       <c r="T58">
-        <v>2.45299955073781</v>
+        <v>2.503086589666601</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.09620694436087</v>
+        <v>3.041887524284363</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09980998655994361</v>
+        <v>0.103131841055143</v>
       </c>
       <c r="C59">
-        <v>155.0018134967903</v>
+        <v>131.8421403646384</v>
       </c>
       <c r="D59">
-        <v>336.4928134967903</v>
+        <v>316.9961403646384</v>
       </c>
       <c r="E59">
-        <v>65.49100000000001</v>
+        <v>69.15400000000002</v>
       </c>
       <c r="F59">
-        <v>208.791</v>
+        <v>212.454</v>
       </c>
       <c r="G59">
         <v>27.3</v>
@@ -6119,45 +6119,45 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M59">
-        <v>13.3835031</v>
+        <v>15.2754426</v>
       </c>
       <c r="N59">
-        <v>27.32760801111111</v>
+        <v>25.4356685111111</v>
       </c>
       <c r="O59">
-        <v>6.558625922666665</v>
+        <v>6.104560442666664</v>
       </c>
       <c r="P59">
-        <v>20.76898208844444</v>
+        <v>19.33110806844444</v>
       </c>
       <c r="Q59">
-        <v>31.16898208844444</v>
+        <v>29.73110806844444</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1675392245580084</v>
+        <v>0.1700912406074834</v>
       </c>
       <c r="T59">
-        <v>2.503086589666601</v>
+        <v>2.555558725687238</v>
       </c>
       <c r="U59">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V59">
         <v>0.24</v>
       </c>
       <c r="W59">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.041887524284363</v>
+        <v>2.665134633225691</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.103131841055143</v>
+        <v>0.1030747355503425</v>
       </c>
       <c r="C60">
-        <v>131.8421403646384</v>
+        <v>128.4951998704819</v>
       </c>
       <c r="D60">
-        <v>316.9961403646383</v>
+        <v>317.3121998704819</v>
       </c>
       <c r="E60">
-        <v>69.15399999999997</v>
+        <v>72.81699999999998</v>
       </c>
       <c r="F60">
-        <v>212.454</v>
+        <v>216.117</v>
       </c>
       <c r="G60">
         <v>27.3</v>
@@ -6201,28 +6201,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M60">
-        <v>15.2754426</v>
+        <v>15.5388123</v>
       </c>
       <c r="N60">
-        <v>25.43566851111111</v>
+        <v>25.17229881111111</v>
       </c>
       <c r="O60">
-        <v>6.104560442666666</v>
+        <v>6.041351714666666</v>
       </c>
       <c r="P60">
-        <v>19.33110806844444</v>
+        <v>19.13094709644444</v>
       </c>
       <c r="Q60">
-        <v>29.73110806844444</v>
+        <v>29.53094709644444</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1700912406074834</v>
+        <v>0.1727677452447377</v>
       </c>
       <c r="T60">
-        <v>2.555558725687238</v>
+        <v>2.610590478099127</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.665134633225692</v>
+        <v>2.619962859781189</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1030747355503425</v>
+        <v>0.1030176300455418</v>
       </c>
       <c r="C61">
-        <v>128.4951998704819</v>
+        <v>125.1488902566194</v>
       </c>
       <c r="D61">
-        <v>317.3121998704819</v>
+        <v>317.6288902566193</v>
       </c>
       <c r="E61">
-        <v>72.81699999999998</v>
+        <v>76.47999999999999</v>
       </c>
       <c r="F61">
-        <v>216.117</v>
+        <v>219.78</v>
       </c>
       <c r="G61">
         <v>27.3</v>
@@ -6283,28 +6283,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M61">
-        <v>15.5388123</v>
+        <v>15.802182</v>
       </c>
       <c r="N61">
-        <v>25.17229881111111</v>
+        <v>24.90892911111111</v>
       </c>
       <c r="O61">
-        <v>6.041351714666666</v>
+        <v>5.978142986666666</v>
       </c>
       <c r="P61">
-        <v>19.13094709644444</v>
+        <v>18.93078612444444</v>
       </c>
       <c r="Q61">
-        <v>29.53094709644444</v>
+        <v>29.33078612444444</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1727677452447377</v>
+        <v>0.1755780751138546</v>
       </c>
       <c r="T61">
-        <v>2.610590478099127</v>
+        <v>2.668373818131609</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.619962859781189</v>
+        <v>2.576296812118168</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1030176300455418</v>
+        <v>0.1029605245407413</v>
       </c>
       <c r="C62">
-        <v>125.1488902566194</v>
+        <v>121.8032134138696</v>
       </c>
       <c r="D62">
-        <v>317.6288902566193</v>
+        <v>317.9462134138696</v>
       </c>
       <c r="E62">
-        <v>76.47999999999999</v>
+        <v>80.143</v>
       </c>
       <c r="F62">
-        <v>219.78</v>
+        <v>223.443</v>
       </c>
       <c r="G62">
         <v>27.3</v>
@@ -6365,28 +6365,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M62">
-        <v>15.802182</v>
+        <v>16.0655517</v>
       </c>
       <c r="N62">
-        <v>24.90892911111111</v>
+        <v>24.6455594111111</v>
       </c>
       <c r="O62">
-        <v>5.978142986666666</v>
+        <v>5.914934258666665</v>
       </c>
       <c r="P62">
-        <v>18.93078612444444</v>
+        <v>18.73062515244444</v>
       </c>
       <c r="Q62">
-        <v>29.33078612444444</v>
+        <v>29.13062515244444</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1755780751138546</v>
+        <v>0.1785325244634392</v>
       </c>
       <c r="T62">
-        <v>2.668373818131609</v>
+        <v>2.729120406370887</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.576296812118168</v>
+        <v>2.534062438149018</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1029605245407413</v>
+        <v>0.1047410990359407</v>
       </c>
       <c r="C63">
-        <v>121.8032134138696</v>
+        <v>108.5352530770296</v>
       </c>
       <c r="D63">
-        <v>317.9462134138696</v>
+        <v>308.3412530770296</v>
       </c>
       <c r="E63">
-        <v>80.143</v>
+        <v>83.80599999999998</v>
       </c>
       <c r="F63">
-        <v>223.443</v>
+        <v>227.106</v>
       </c>
       <c r="G63">
         <v>27.3</v>
@@ -6447,45 +6447,45 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M63">
-        <v>16.0655517</v>
+        <v>17.2146348</v>
       </c>
       <c r="N63">
-        <v>24.6455594111111</v>
+        <v>23.49647631111111</v>
       </c>
       <c r="O63">
-        <v>5.914934258666665</v>
+        <v>5.639154314666666</v>
       </c>
       <c r="P63">
-        <v>18.73062515244444</v>
+        <v>17.85732199644444</v>
       </c>
       <c r="Q63">
-        <v>29.13062515244444</v>
+        <v>28.25732199644444</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1785325244634392</v>
+        <v>0.1816424711472124</v>
       </c>
       <c r="T63">
-        <v>2.729120406370887</v>
+        <v>2.793064183464863</v>
       </c>
       <c r="U63">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V63">
         <v>0.24</v>
       </c>
       <c r="W63">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.534062438149018</v>
+        <v>2.364912853748782</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1047410990359407</v>
+        <v>0.1047136335311401</v>
       </c>
       <c r="C64">
-        <v>108.5352530770296</v>
+        <v>105.0160016061732</v>
       </c>
       <c r="D64">
-        <v>308.3412530770296</v>
+        <v>308.4850016061732</v>
       </c>
       <c r="E64">
-        <v>83.80599999999998</v>
+        <v>87.46899999999999</v>
       </c>
       <c r="F64">
-        <v>227.106</v>
+        <v>230.769</v>
       </c>
       <c r="G64">
         <v>27.3</v>
@@ -6529,28 +6529,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M64">
-        <v>17.2146348</v>
+        <v>17.4922902</v>
       </c>
       <c r="N64">
-        <v>23.49647631111111</v>
+        <v>23.21882091111111</v>
       </c>
       <c r="O64">
-        <v>5.639154314666666</v>
+        <v>5.572517018666665</v>
       </c>
       <c r="P64">
-        <v>17.85732199644444</v>
+        <v>17.64630389244444</v>
       </c>
       <c r="Q64">
-        <v>28.25732199644444</v>
+        <v>28.04630389244444</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1816424711472124</v>
+        <v>0.1849205230571354</v>
       </c>
       <c r="T64">
-        <v>2.793064183464863</v>
+        <v>2.860464380942296</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.364912853748782</v>
+        <v>2.327374554482929</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1047136335311401</v>
+        <v>0.1046861680263395</v>
       </c>
       <c r="C65">
-        <v>105.0160016061732</v>
+        <v>101.4968842288077</v>
       </c>
       <c r="D65">
-        <v>308.4850016061732</v>
+        <v>308.6288842288077</v>
       </c>
       <c r="E65">
-        <v>87.46899999999999</v>
+        <v>91.13200000000001</v>
       </c>
       <c r="F65">
-        <v>230.769</v>
+        <v>234.432</v>
       </c>
       <c r="G65">
         <v>27.3</v>
@@ -6611,28 +6611,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M65">
-        <v>17.4922902</v>
+        <v>17.7699456</v>
       </c>
       <c r="N65">
-        <v>23.21882091111111</v>
+        <v>22.94116551111111</v>
       </c>
       <c r="O65">
-        <v>5.572517018666665</v>
+        <v>5.505879722666665</v>
       </c>
       <c r="P65">
-        <v>17.64630389244444</v>
+        <v>17.43528578844444</v>
       </c>
       <c r="Q65">
-        <v>28.04630389244444</v>
+        <v>27.83528578844444</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1849205230571354</v>
+        <v>0.1883806889620542</v>
       </c>
       <c r="T65">
-        <v>2.860464380942296</v>
+        <v>2.931609033835143</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.327374554482929</v>
+        <v>2.291009327069133</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1046861680263395</v>
+        <v>0.1046587025215389</v>
       </c>
       <c r="C66">
-        <v>101.4968842288077</v>
+        <v>97.97790113265091</v>
       </c>
       <c r="D66">
-        <v>308.6288842288077</v>
+        <v>308.7729011326509</v>
       </c>
       <c r="E66">
-        <v>91.13200000000001</v>
+        <v>94.79500000000002</v>
       </c>
       <c r="F66">
-        <v>234.432</v>
+        <v>238.095</v>
       </c>
       <c r="G66">
         <v>27.3</v>
@@ -6693,28 +6693,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M66">
-        <v>17.7699456</v>
+        <v>18.047601</v>
       </c>
       <c r="N66">
-        <v>22.94116551111111</v>
+        <v>22.6635101111111</v>
       </c>
       <c r="O66">
-        <v>5.505879722666665</v>
+        <v>5.439242426666665</v>
       </c>
       <c r="P66">
-        <v>17.43528578844444</v>
+        <v>17.22426768444444</v>
       </c>
       <c r="Q66">
-        <v>27.83528578844444</v>
+        <v>27.62426768444444</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1883806889620542</v>
+        <v>0.1920385786329684</v>
       </c>
       <c r="T66">
-        <v>2.931609033835143</v>
+        <v>3.006819095464725</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.291009327069133</v>
+        <v>2.255763029729608</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1046587025215389</v>
+        <v>0.1046312370167383</v>
       </c>
       <c r="C67">
-        <v>97.97790113265091</v>
+        <v>94.45905250577167</v>
       </c>
       <c r="D67">
-        <v>308.7729011326509</v>
+        <v>308.9170525057717</v>
       </c>
       <c r="E67">
-        <v>94.79500000000002</v>
+        <v>98.458</v>
       </c>
       <c r="F67">
-        <v>238.095</v>
+        <v>241.758</v>
       </c>
       <c r="G67">
         <v>27.3</v>
@@ -6775,28 +6775,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M67">
-        <v>18.047601</v>
+        <v>18.3252564</v>
       </c>
       <c r="N67">
-        <v>22.6635101111111</v>
+        <v>22.38585471111111</v>
       </c>
       <c r="O67">
-        <v>5.439242426666665</v>
+        <v>5.372605130666666</v>
       </c>
       <c r="P67">
-        <v>17.22426768444444</v>
+        <v>17.01324958044444</v>
       </c>
       <c r="Q67">
-        <v>27.62426768444444</v>
+        <v>27.41324958044444</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1920385786329684</v>
+        <v>0.1959116382845246</v>
       </c>
       <c r="T67">
-        <v>3.006819095464725</v>
+        <v>3.086453278366634</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.255763029729608</v>
+        <v>2.221584802006432</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1046312370167383</v>
+        <v>0.1046037715119378</v>
       </c>
       <c r="C68">
-        <v>94.45905250577167</v>
+        <v>90.94033853658945</v>
       </c>
       <c r="D68">
-        <v>308.9170525057717</v>
+        <v>309.0613385365895</v>
       </c>
       <c r="E68">
-        <v>98.458</v>
+        <v>102.121</v>
       </c>
       <c r="F68">
-        <v>241.758</v>
+        <v>245.421</v>
       </c>
       <c r="G68">
         <v>27.3</v>
@@ -6857,28 +6857,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M68">
-        <v>18.3252564</v>
+        <v>18.6029118</v>
       </c>
       <c r="N68">
-        <v>22.38585471111111</v>
+        <v>22.1081993111111</v>
       </c>
       <c r="O68">
-        <v>5.372605130666666</v>
+        <v>5.305967834666665</v>
       </c>
       <c r="P68">
-        <v>17.01324958044444</v>
+        <v>16.80223147644444</v>
       </c>
       <c r="Q68">
-        <v>27.41324958044444</v>
+        <v>27.20223147644444</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1959116382845246</v>
+        <v>0.2000194288240539</v>
       </c>
       <c r="T68">
-        <v>3.086453278366634</v>
+        <v>3.170913775383811</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.221584802006432</v>
+        <v>2.188426819886933</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1046037715119378</v>
+        <v>0.1045763060071372</v>
       </c>
       <c r="C69">
-        <v>90.94033853658945</v>
+        <v>87.42175941387669</v>
       </c>
       <c r="D69">
-        <v>309.0613385365895</v>
+        <v>309.2057594138767</v>
       </c>
       <c r="E69">
-        <v>102.121</v>
+        <v>105.784</v>
       </c>
       <c r="F69">
-        <v>245.421</v>
+        <v>249.084</v>
       </c>
       <c r="G69">
         <v>27.3</v>
@@ -6939,28 +6939,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M69">
-        <v>18.6029118</v>
+        <v>18.88056720000001</v>
       </c>
       <c r="N69">
-        <v>22.1081993111111</v>
+        <v>21.8305439111111</v>
       </c>
       <c r="O69">
-        <v>5.305967834666665</v>
+        <v>5.239330538666665</v>
       </c>
       <c r="P69">
-        <v>16.80223147644444</v>
+        <v>16.59121337244444</v>
       </c>
       <c r="Q69">
-        <v>27.20223147644444</v>
+        <v>26.99121337244444</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2000194288240539</v>
+        <v>0.2043839562723037</v>
       </c>
       <c r="T69">
-        <v>3.170913775383811</v>
+        <v>3.260653053464561</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.188426819886933</v>
+        <v>2.156244072535654</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1045763060071372</v>
+        <v>0.1045488405023366</v>
       </c>
       <c r="C70">
-        <v>87.42175941387669</v>
+        <v>83.90331532675825</v>
       </c>
       <c r="D70">
-        <v>309.2057594138767</v>
+        <v>309.3503153267583</v>
       </c>
       <c r="E70">
-        <v>105.784</v>
+        <v>109.447</v>
       </c>
       <c r="F70">
-        <v>249.084</v>
+        <v>252.747</v>
       </c>
       <c r="G70">
         <v>27.3</v>
@@ -7021,28 +7021,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M70">
-        <v>18.88056720000001</v>
+        <v>19.15822260000001</v>
       </c>
       <c r="N70">
-        <v>21.8305439111111</v>
+        <v>21.5528885111111</v>
       </c>
       <c r="O70">
-        <v>5.239330538666665</v>
+        <v>5.172693242666664</v>
       </c>
       <c r="P70">
-        <v>16.59121337244444</v>
+        <v>16.38019526844444</v>
       </c>
       <c r="Q70">
-        <v>26.99121337244444</v>
+        <v>26.78019526844444</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2043839562723037</v>
+        <v>0.2090300661365697</v>
       </c>
       <c r="T70">
-        <v>3.260653053464561</v>
+        <v>3.356181962389231</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.156244072535654</v>
+        <v>2.124994158440935</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1045488405023366</v>
+        <v>0.104521374997536</v>
       </c>
       <c r="C71">
-        <v>83.90331532675825</v>
+        <v>80.38500646471317</v>
       </c>
       <c r="D71">
-        <v>309.3503153267583</v>
+        <v>309.4950064647132</v>
       </c>
       <c r="E71">
-        <v>109.447</v>
+        <v>113.11</v>
       </c>
       <c r="F71">
-        <v>252.747</v>
+        <v>256.41</v>
       </c>
       <c r="G71">
         <v>27.3</v>
@@ -7103,28 +7103,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M71">
-        <v>19.15822260000001</v>
+        <v>19.435878</v>
       </c>
       <c r="N71">
-        <v>21.5528885111111</v>
+        <v>21.27523311111111</v>
       </c>
       <c r="O71">
-        <v>5.172693242666664</v>
+        <v>5.106055946666666</v>
       </c>
       <c r="P71">
-        <v>16.38019526844444</v>
+        <v>16.16917716444444</v>
       </c>
       <c r="Q71">
-        <v>26.78019526844444</v>
+        <v>26.56917716444444</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2090300661365697</v>
+        <v>0.2139859166584534</v>
       </c>
       <c r="T71">
-        <v>3.356181962389231</v>
+        <v>3.458079465242212</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.124994158440935</v>
+        <v>2.094637099034636</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.104521374997536</v>
+        <v>0.1044939094927354</v>
       </c>
       <c r="C72">
-        <v>80.38500646471317</v>
+        <v>76.86683301757495</v>
       </c>
       <c r="D72">
-        <v>309.4950064647132</v>
+        <v>309.639833017575</v>
       </c>
       <c r="E72">
-        <v>113.11</v>
+        <v>116.773</v>
       </c>
       <c r="F72">
-        <v>256.41</v>
+        <v>260.073</v>
       </c>
       <c r="G72">
         <v>27.3</v>
@@ -7185,28 +7185,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M72">
-        <v>19.435878</v>
+        <v>19.7135334</v>
       </c>
       <c r="N72">
-        <v>21.27523311111111</v>
+        <v>20.99757771111111</v>
       </c>
       <c r="O72">
-        <v>5.106055946666666</v>
+        <v>5.039418650666665</v>
       </c>
       <c r="P72">
-        <v>16.16917716444444</v>
+        <v>15.95815906044444</v>
       </c>
       <c r="Q72">
-        <v>26.56917716444444</v>
+        <v>26.35815906044444</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2139859166584534</v>
+        <v>0.2192835499749498</v>
       </c>
       <c r="T72">
-        <v>3.458079465242212</v>
+        <v>3.567004382085054</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.094637099034636</v>
+        <v>2.065135168062317</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1044939094927354</v>
+        <v>0.1044664439879349</v>
       </c>
       <c r="C73">
-        <v>76.866833017575</v>
+        <v>73.3487951755327</v>
       </c>
       <c r="D73">
-        <v>309.639833017575</v>
+        <v>309.7847951755327</v>
       </c>
       <c r="E73">
-        <v>116.773</v>
+        <v>120.436</v>
       </c>
       <c r="F73">
-        <v>260.073</v>
+        <v>263.736</v>
       </c>
       <c r="G73">
         <v>27.3</v>
@@ -7267,28 +7267,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M73">
-        <v>19.7135334</v>
+        <v>19.9911888</v>
       </c>
       <c r="N73">
-        <v>20.99757771111111</v>
+        <v>20.71992231111111</v>
       </c>
       <c r="O73">
-        <v>5.039418650666666</v>
+        <v>4.972781354666666</v>
       </c>
       <c r="P73">
-        <v>15.95815906044444</v>
+        <v>15.74714095644444</v>
       </c>
       <c r="Q73">
-        <v>26.35815906044444</v>
+        <v>26.14714095644444</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2192835499749498</v>
+        <v>0.2249595856711959</v>
       </c>
       <c r="T73">
-        <v>3.567004382085052</v>
+        <v>3.683709650130954</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.065135168062318</v>
+        <v>2.036452735172563</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1044664439879349</v>
+        <v>0.1044389784831343</v>
       </c>
       <c r="C74">
-        <v>73.3487951755327</v>
+        <v>69.83089312913177</v>
       </c>
       <c r="D74">
-        <v>309.7847951755327</v>
+        <v>309.9298931291318</v>
       </c>
       <c r="E74">
-        <v>120.436</v>
+        <v>124.099</v>
       </c>
       <c r="F74">
-        <v>263.736</v>
+        <v>267.399</v>
       </c>
       <c r="G74">
         <v>27.3</v>
@@ -7349,28 +7349,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M74">
-        <v>19.9911888</v>
+        <v>20.2688442</v>
       </c>
       <c r="N74">
-        <v>20.71992231111111</v>
+        <v>20.44226691111111</v>
       </c>
       <c r="O74">
-        <v>4.972781354666666</v>
+        <v>4.906144058666666</v>
       </c>
       <c r="P74">
-        <v>15.74714095644444</v>
+        <v>15.53612285244444</v>
       </c>
       <c r="Q74">
-        <v>26.14714095644444</v>
+        <v>25.93612285244444</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2249595856711959</v>
+        <v>0.2310560684560528</v>
       </c>
       <c r="T74">
-        <v>3.683709650130954</v>
+        <v>3.809059752846922</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.036452735172563</v>
+        <v>2.00855612236198</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1044389784831343</v>
+        <v>0.1123975929783337</v>
       </c>
       <c r="C75">
-        <v>69.83089312913177</v>
+        <v>29.13033021367346</v>
       </c>
       <c r="D75">
-        <v>309.9298931291318</v>
+        <v>272.8923302136735</v>
       </c>
       <c r="E75">
-        <v>124.099</v>
+        <v>127.762</v>
       </c>
       <c r="F75">
-        <v>267.399</v>
+        <v>271.062</v>
       </c>
       <c r="G75">
         <v>27.3</v>
@@ -7431,45 +7431,45 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M75">
-        <v>20.2688442</v>
+        <v>24.39558</v>
       </c>
       <c r="N75">
-        <v>20.44226691111111</v>
+        <v>16.31553111111111</v>
       </c>
       <c r="O75">
-        <v>4.906144058666666</v>
+        <v>3.915727466666666</v>
       </c>
       <c r="P75">
-        <v>15.53612285244444</v>
+        <v>12.39980364444444</v>
       </c>
       <c r="Q75">
-        <v>25.93612285244444</v>
+        <v>22.79980364444444</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2310560684560528</v>
+        <v>0.2376215114551295</v>
       </c>
       <c r="T75">
-        <v>3.809059752846922</v>
+        <v>3.944052171156426</v>
       </c>
       <c r="U75">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V75">
         <v>0.24</v>
       </c>
       <c r="W75">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y75">
-        <v>2.00855612236198</v>
+        <v>1.668790457579246</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1123975929783337</v>
+        <v>0.1124780474735331</v>
       </c>
       <c r="C76">
-        <v>29.13033021367346</v>
+        <v>25.13805520483572</v>
       </c>
       <c r="D76">
-        <v>272.8923302136735</v>
+        <v>272.5630552048357</v>
       </c>
       <c r="E76">
-        <v>127.762</v>
+        <v>131.425</v>
       </c>
       <c r="F76">
-        <v>271.062</v>
+        <v>274.725</v>
       </c>
       <c r="G76">
         <v>27.3</v>
@@ -7513,28 +7513,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M76">
-        <v>24.39558</v>
+        <v>24.72525</v>
       </c>
       <c r="N76">
-        <v>16.31553111111111</v>
+        <v>15.98586111111111</v>
       </c>
       <c r="O76">
-        <v>3.915727466666666</v>
+        <v>3.836606666666665</v>
       </c>
       <c r="P76">
-        <v>12.39980364444444</v>
+        <v>12.14925444444444</v>
       </c>
       <c r="Q76">
-        <v>22.79980364444444</v>
+        <v>22.54925444444444</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2376215114551295</v>
+        <v>0.2447121898941323</v>
       </c>
       <c r="T76">
-        <v>3.944052171156426</v>
+        <v>4.089843982930692</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.668790457579246</v>
+        <v>1.646539918144856</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1124780474735331</v>
+        <v>0.1125585019687325</v>
       </c>
       <c r="C77">
-        <v>25.13805520483572</v>
+        <v>21.14657385235142</v>
       </c>
       <c r="D77">
-        <v>272.5630552048357</v>
+        <v>272.2345738523514</v>
       </c>
       <c r="E77">
-        <v>131.425</v>
+        <v>135.088</v>
       </c>
       <c r="F77">
-        <v>274.725</v>
+        <v>278.388</v>
       </c>
       <c r="G77">
         <v>27.3</v>
@@ -7595,28 +7595,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M77">
-        <v>24.72525</v>
+        <v>25.05492</v>
       </c>
       <c r="N77">
-        <v>15.98586111111111</v>
+        <v>15.65619111111111</v>
       </c>
       <c r="O77">
-        <v>3.836606666666665</v>
+        <v>3.757485866666665</v>
       </c>
       <c r="P77">
-        <v>12.14925444444444</v>
+        <v>11.89870524444444</v>
       </c>
       <c r="Q77">
-        <v>22.54925444444444</v>
+        <v>22.29870524444444</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2447121898941323</v>
+        <v>0.2523937582030521</v>
       </c>
       <c r="T77">
-        <v>4.089843982930692</v>
+        <v>4.247785112352812</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.646539918144856</v>
+        <v>1.624874919221897</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1125585019687325</v>
+        <v>0.1126389564639319</v>
       </c>
       <c r="C78">
-        <v>21.14657385235142</v>
+        <v>17.1558832902324</v>
       </c>
       <c r="D78">
-        <v>272.2345738523514</v>
+        <v>271.9068832902324</v>
       </c>
       <c r="E78">
-        <v>135.088</v>
+        <v>138.751</v>
       </c>
       <c r="F78">
-        <v>278.388</v>
+        <v>282.051</v>
       </c>
       <c r="G78">
         <v>27.3</v>
@@ -7677,28 +7677,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M78">
-        <v>25.05492</v>
+        <v>25.38459</v>
       </c>
       <c r="N78">
-        <v>15.65619111111111</v>
+        <v>15.32652111111111</v>
       </c>
       <c r="O78">
-        <v>3.757485866666665</v>
+        <v>3.678365066666666</v>
       </c>
       <c r="P78">
-        <v>11.89870524444444</v>
+        <v>11.64815604444444</v>
       </c>
       <c r="Q78">
-        <v>22.29870524444444</v>
+        <v>22.04815604444444</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2523937582030521</v>
+        <v>0.260743288973617</v>
       </c>
       <c r="T78">
-        <v>4.247785112352812</v>
+        <v>4.41946025302903</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.624874919221897</v>
+        <v>1.603772647543691</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1126389564639319</v>
+        <v>0.1127194109591313</v>
       </c>
       <c r="C79">
-        <v>17.1558832902324</v>
+        <v>13.1659806662729</v>
       </c>
       <c r="D79">
-        <v>271.9068832902324</v>
+        <v>271.5799806662729</v>
       </c>
       <c r="E79">
-        <v>138.751</v>
+        <v>142.414</v>
       </c>
       <c r="F79">
-        <v>282.051</v>
+        <v>285.714</v>
       </c>
       <c r="G79">
         <v>27.3</v>
@@ -7759,28 +7759,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M79">
-        <v>25.38459</v>
+        <v>25.71426</v>
       </c>
       <c r="N79">
-        <v>15.32652111111111</v>
+        <v>14.99685111111111</v>
       </c>
       <c r="O79">
-        <v>3.678365066666666</v>
+        <v>3.599244266666666</v>
       </c>
       <c r="P79">
-        <v>11.64815604444444</v>
+        <v>11.39760684444444</v>
       </c>
       <c r="Q79">
-        <v>22.04815604444444</v>
+        <v>21.79760684444444</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.260743288973617</v>
+        <v>0.2698518679960515</v>
       </c>
       <c r="T79">
-        <v>4.41946025302903</v>
+        <v>4.606742224675813</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.603772647543691</v>
+        <v>1.58321145975467</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1127194109591313</v>
+        <v>0.1127998654543308</v>
       </c>
       <c r="C80">
-        <v>13.1659806662729</v>
+        <v>9.176863141967317</v>
       </c>
       <c r="D80">
-        <v>271.5799806662729</v>
+        <v>271.2538631419673</v>
       </c>
       <c r="E80">
-        <v>142.414</v>
+        <v>146.077</v>
       </c>
       <c r="F80">
-        <v>285.714</v>
+        <v>289.377</v>
       </c>
       <c r="G80">
         <v>27.3</v>
@@ -7841,28 +7841,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M80">
-        <v>25.71426</v>
+        <v>26.04393</v>
       </c>
       <c r="N80">
-        <v>14.99685111111111</v>
+        <v>14.66718111111111</v>
       </c>
       <c r="O80">
-        <v>3.599244266666666</v>
+        <v>3.520123466666666</v>
       </c>
       <c r="P80">
-        <v>11.39760684444444</v>
+        <v>11.14705764444444</v>
       </c>
       <c r="Q80">
-        <v>21.79760684444444</v>
+        <v>21.54705764444444</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2698518679960515</v>
+        <v>0.2798279307349084</v>
       </c>
       <c r="T80">
-        <v>4.606742224675813</v>
+        <v>4.811860574574671</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.58321145975467</v>
+        <v>1.56317080836537</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1127998654543308</v>
+        <v>0.1128803199495302</v>
       </c>
       <c r="C81">
-        <v>9.176863141967317</v>
+        <v>5.188527892427715</v>
       </c>
       <c r="D81">
-        <v>271.2538631419673</v>
+        <v>270.9285278924277</v>
       </c>
       <c r="E81">
-        <v>146.077</v>
+        <v>149.74</v>
       </c>
       <c r="F81">
-        <v>289.377</v>
+        <v>293.04</v>
       </c>
       <c r="G81">
         <v>27.3</v>
@@ -7923,28 +7923,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M81">
-        <v>26.04393</v>
+        <v>26.3736</v>
       </c>
       <c r="N81">
-        <v>14.66718111111111</v>
+        <v>14.33751111111111</v>
       </c>
       <c r="O81">
-        <v>3.520123466666666</v>
+        <v>3.441002666666666</v>
       </c>
       <c r="P81">
-        <v>11.14705764444444</v>
+        <v>10.89650844444444</v>
       </c>
       <c r="Q81">
-        <v>21.54705764444444</v>
+        <v>21.29650844444444</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2798279307349084</v>
+        <v>0.2908015997476509</v>
       </c>
       <c r="T81">
-        <v>4.811860574574671</v>
+        <v>5.037490759463414</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.56317080836537</v>
+        <v>1.543631173260803</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1128803199495302</v>
+        <v>0.1129607744447296</v>
       </c>
       <c r="C82">
-        <v>5.188527892427715</v>
+        <v>1.200972106302061</v>
       </c>
       <c r="D82">
-        <v>270.9285278924277</v>
+        <v>270.6039721063021</v>
       </c>
       <c r="E82">
-        <v>149.74</v>
+        <v>153.403</v>
       </c>
       <c r="F82">
-        <v>293.04</v>
+        <v>296.703</v>
       </c>
       <c r="G82">
         <v>27.3</v>
@@ -8005,28 +8005,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M82">
-        <v>26.3736</v>
+        <v>26.70327</v>
       </c>
       <c r="N82">
-        <v>14.33751111111111</v>
+        <v>14.00784111111111</v>
       </c>
       <c r="O82">
-        <v>3.441002666666666</v>
+        <v>3.361881866666665</v>
       </c>
       <c r="P82">
-        <v>10.89650844444444</v>
+        <v>10.64595924444444</v>
       </c>
       <c r="Q82">
-        <v>21.29650844444444</v>
+        <v>21.04595924444444</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2908015997476509</v>
+        <v>0.3029303918143663</v>
       </c>
       <c r="T82">
-        <v>5.037490759463414</v>
+        <v>5.28687149012992</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.543631173260803</v>
+        <v>1.524573998282274</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1129607744447296</v>
+        <v>0.113041228939929</v>
       </c>
       <c r="C83">
-        <v>1.200972106302061</v>
+        <v>-2.785807014305817</v>
       </c>
       <c r="D83">
-        <v>270.6039721063021</v>
+        <v>270.2801929856942</v>
       </c>
       <c r="E83">
-        <v>153.403</v>
+        <v>157.066</v>
       </c>
       <c r="F83">
-        <v>296.703</v>
+        <v>300.366</v>
       </c>
       <c r="G83">
         <v>27.3</v>
@@ -8087,28 +8087,28 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M83">
-        <v>26.70327</v>
+        <v>27.03294</v>
       </c>
       <c r="N83">
-        <v>14.00784111111111</v>
+        <v>13.67817111111111</v>
       </c>
       <c r="O83">
-        <v>3.361881866666665</v>
+        <v>3.282761066666665</v>
       </c>
       <c r="P83">
-        <v>10.64595924444444</v>
+        <v>10.39541004444444</v>
       </c>
       <c r="Q83">
-        <v>21.04595924444444</v>
+        <v>20.79541004444444</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3029303918143663</v>
+        <v>0.3164068274440501</v>
       </c>
       <c r="T83">
-        <v>5.28687149012992</v>
+        <v>5.563961190870482</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.524573998282274</v>
+        <v>1.505981632449564</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.113041228939929</v>
+        <v>0.1525808463296932</v>
       </c>
       <c r="C84">
-        <v>-2.785807014305817</v>
+        <v>-106.5301960088247</v>
       </c>
       <c r="D84">
-        <v>270.2801929856942</v>
+        <v>170.1988039911753</v>
       </c>
       <c r="E84">
-        <v>157.066</v>
+        <v>160.729</v>
       </c>
       <c r="F84">
-        <v>300.366</v>
+        <v>304.0290000000001</v>
       </c>
       <c r="G84">
         <v>27.3</v>
@@ -8169,45 +8169,45 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M84">
-        <v>27.03294</v>
+        <v>44.63145720000001</v>
       </c>
       <c r="N84">
-        <v>13.67817111111111</v>
+        <v>-3.920346088888905</v>
       </c>
       <c r="O84">
-        <v>3.282761066666665</v>
+        <v>-0.9408830613333373</v>
       </c>
       <c r="P84">
-        <v>10.39541004444444</v>
+        <v>-2.979463027555568</v>
       </c>
       <c r="Q84">
-        <v>20.79541004444444</v>
+        <v>7.420536972444431</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3164068274440501</v>
+        <v>0.3377105470802343</v>
       </c>
       <c r="T84">
-        <v>5.563961190870482</v>
+        <v>6.001988089143854</v>
       </c>
       <c r="U84">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.24</v>
+        <v>0.2189188361671208</v>
       </c>
       <c r="W84">
-        <v>0.0684</v>
+        <v>0.1146627148506667</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y84">
-        <v>1.505981632449564</v>
+        <v>0.9121618173630033</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1525808463296932</v>
+        <v>0.1535908463296932</v>
       </c>
       <c r="C85">
-        <v>-106.5301960088247</v>
+        <v>-111.7879584388859</v>
       </c>
       <c r="D85">
-        <v>170.1988039911753</v>
+        <v>168.6040415611141</v>
       </c>
       <c r="E85">
-        <v>160.729</v>
+        <v>164.3920000000001</v>
       </c>
       <c r="F85">
-        <v>304.0290000000001</v>
+        <v>307.6920000000001</v>
       </c>
       <c r="G85">
         <v>27.3</v>
@@ -8251,37 +8251,37 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M85">
-        <v>44.63145720000001</v>
+        <v>45.16918560000001</v>
       </c>
       <c r="N85">
-        <v>-3.920346088888905</v>
+        <v>-4.458074488888904</v>
       </c>
       <c r="O85">
-        <v>-0.9408830613333373</v>
+        <v>-1.069937877333337</v>
       </c>
       <c r="P85">
-        <v>-2.979463027555568</v>
+        <v>-3.388136611555567</v>
       </c>
       <c r="Q85">
-        <v>7.420536972444431</v>
+        <v>7.011863388444431</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3377105470802343</v>
+        <v>0.3559549562727491</v>
       </c>
       <c r="T85">
-        <v>6.001988089143854</v>
+        <v>6.377112344715346</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2189188361671208</v>
+        <v>0.2163126595460836</v>
       </c>
       <c r="W85">
-        <v>0.1146627148506667</v>
+        <v>0.1150453015786349</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9121618173630033</v>
+        <v>0.9013027481086818</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1535908463296932</v>
+        <v>0.1546008463296932</v>
       </c>
       <c r="C86">
-        <v>-111.7879584388859</v>
+        <v>-117.0161124585587</v>
       </c>
       <c r="D86">
-        <v>168.6040415611141</v>
+        <v>167.0388875414413</v>
       </c>
       <c r="E86">
-        <v>164.392</v>
+        <v>168.055</v>
       </c>
       <c r="F86">
-        <v>307.692</v>
+        <v>311.355</v>
       </c>
       <c r="G86">
         <v>27.3</v>
@@ -8333,37 +8333,37 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M86">
-        <v>45.16918560000001</v>
+        <v>45.706914</v>
       </c>
       <c r="N86">
-        <v>-4.458074488888897</v>
+        <v>-4.995802888888896</v>
       </c>
       <c r="O86">
-        <v>-1.069937877333335</v>
+        <v>-1.198992693333335</v>
       </c>
       <c r="P86">
-        <v>-3.388136611555562</v>
+        <v>-3.796810195555561</v>
       </c>
       <c r="Q86">
-        <v>7.011863388444437</v>
+        <v>6.603189804444438</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3559549562727489</v>
+        <v>0.3766319533575988</v>
       </c>
       <c r="T86">
-        <v>6.377112344715342</v>
+        <v>6.802253167696365</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2163126595460837</v>
+        <v>0.2137678047278944</v>
       </c>
       <c r="W86">
-        <v>0.1150453015786349</v>
+        <v>0.1154188862659451</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9013027481086819</v>
+        <v>0.8906991863662269</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1546008463296932</v>
+        <v>0.1556108463296932</v>
       </c>
       <c r="C87">
-        <v>-117.0161124585587</v>
+        <v>-122.2154750498306</v>
       </c>
       <c r="D87">
-        <v>167.0388875414413</v>
+        <v>165.5025249501694</v>
       </c>
       <c r="E87">
-        <v>168.055</v>
+        <v>171.718</v>
       </c>
       <c r="F87">
-        <v>311.355</v>
+        <v>315.018</v>
       </c>
       <c r="G87">
         <v>27.3</v>
@@ -8415,37 +8415,37 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M87">
-        <v>45.706914</v>
+        <v>46.24464240000001</v>
       </c>
       <c r="N87">
-        <v>-4.995802888888896</v>
+        <v>-5.533531288888902</v>
       </c>
       <c r="O87">
-        <v>-1.198992693333335</v>
+        <v>-1.328047509333336</v>
       </c>
       <c r="P87">
-        <v>-3.796810195555561</v>
+        <v>-4.205483779555566</v>
       </c>
       <c r="Q87">
-        <v>6.603189804444438</v>
+        <v>6.194516220444433</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3766319533575988</v>
+        <v>0.4002628071688559</v>
       </c>
       <c r="T87">
-        <v>6.802253167696365</v>
+        <v>7.288128393960391</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2137678047278944</v>
+        <v>0.2112821325798956</v>
       </c>
       <c r="W87">
-        <v>0.1154188862659451</v>
+        <v>0.1157837829372713</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8906991863662269</v>
+        <v>0.8803422190828986</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1556108463296932</v>
+        <v>0.1566208463296931</v>
       </c>
       <c r="C88">
-        <v>-122.2154750498306</v>
+        <v>-127.3868334114187</v>
       </c>
       <c r="D88">
-        <v>165.5025249501694</v>
+        <v>163.9941665885812</v>
       </c>
       <c r="E88">
-        <v>171.718</v>
+        <v>175.381</v>
       </c>
       <c r="F88">
-        <v>315.018</v>
+        <v>318.681</v>
       </c>
       <c r="G88">
         <v>27.3</v>
@@ -8497,37 +8497,37 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M88">
-        <v>46.24464240000001</v>
+        <v>46.7823708</v>
       </c>
       <c r="N88">
-        <v>-5.533531288888902</v>
+        <v>-6.071259688888894</v>
       </c>
       <c r="O88">
-        <v>-1.328047509333336</v>
+        <v>-1.457102325333334</v>
       </c>
       <c r="P88">
-        <v>-4.205483779555566</v>
+        <v>-4.614157363555559</v>
       </c>
       <c r="Q88">
-        <v>6.194516220444433</v>
+        <v>5.785842636444439</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4002628071688559</v>
+        <v>0.4275291769510755</v>
       </c>
       <c r="T88">
-        <v>7.288128393960391</v>
+        <v>7.848753655034267</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2112821325798956</v>
+        <v>0.2088536023203567</v>
       </c>
       <c r="W88">
-        <v>0.1157837829372713</v>
+        <v>0.1161402911793716</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8803422190828986</v>
+        <v>0.8702233430014861</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1566208463296931</v>
+        <v>0.1576308463296932</v>
       </c>
       <c r="C89">
-        <v>-127.3868334114187</v>
+        <v>-132.5309463037075</v>
       </c>
       <c r="D89">
-        <v>163.9941665885812</v>
+        <v>162.5130536962924</v>
       </c>
       <c r="E89">
-        <v>175.381</v>
+        <v>179.044</v>
       </c>
       <c r="F89">
-        <v>318.681</v>
+        <v>322.344</v>
       </c>
       <c r="G89">
         <v>27.3</v>
@@ -8579,37 +8579,37 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M89">
-        <v>46.7823708</v>
+        <v>47.3200992</v>
       </c>
       <c r="N89">
-        <v>-6.071259688888894</v>
+        <v>-6.608988088888893</v>
       </c>
       <c r="O89">
-        <v>-1.457102325333334</v>
+        <v>-1.586157141333334</v>
       </c>
       <c r="P89">
-        <v>-4.614157363555559</v>
+        <v>-5.022830947555558</v>
       </c>
       <c r="Q89">
-        <v>5.785842636444439</v>
+        <v>5.37716905244444</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4275291769510755</v>
+        <v>0.4593399416969986</v>
       </c>
       <c r="T89">
-        <v>7.848753655034267</v>
+        <v>8.502816459620458</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2088536023203567</v>
+        <v>0.2064802659303526</v>
       </c>
       <c r="W89">
-        <v>0.1161402911793716</v>
+        <v>0.1164886969614242</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8702233430014861</v>
+        <v>0.8603344413764692</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1576308463296932</v>
+        <v>0.1586408463296932</v>
       </c>
       <c r="C90">
-        <v>-132.5309463037075</v>
+        <v>-137.6485453214576</v>
       </c>
       <c r="D90">
-        <v>162.5130536962924</v>
+        <v>161.0584546785424</v>
       </c>
       <c r="E90">
-        <v>179.044</v>
+        <v>182.707</v>
       </c>
       <c r="F90">
-        <v>322.344</v>
+        <v>326.007</v>
       </c>
       <c r="G90">
         <v>27.3</v>
@@ -8661,37 +8661,37 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M90">
-        <v>47.3200992</v>
+        <v>47.85782760000001</v>
       </c>
       <c r="N90">
-        <v>-6.608988088888893</v>
+        <v>-7.146716488888899</v>
       </c>
       <c r="O90">
-        <v>-1.586157141333334</v>
+        <v>-1.715211957333336</v>
       </c>
       <c r="P90">
-        <v>-5.022830947555558</v>
+        <v>-5.431504531555563</v>
       </c>
       <c r="Q90">
-        <v>5.37716905244444</v>
+        <v>4.968495468444435</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4593399416969986</v>
+        <v>0.4969344818512712</v>
       </c>
       <c r="T90">
-        <v>8.502816459620458</v>
+        <v>9.275799774131409</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2064802659303526</v>
+        <v>0.2041602629423711</v>
       </c>
       <c r="W90">
-        <v>0.1164886969614242</v>
+        <v>0.1168292734000599</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8603344413764692</v>
+        <v>0.8506677622598795</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1586408463296932</v>
+        <v>0.1596508463296932</v>
       </c>
       <c r="C91">
-        <v>-137.6485453214576</v>
+        <v>-142.7403360987722</v>
       </c>
       <c r="D91">
-        <v>161.0584546785424</v>
+        <v>159.6296639012278</v>
       </c>
       <c r="E91">
-        <v>182.707</v>
+        <v>186.37</v>
       </c>
       <c r="F91">
-        <v>326.007</v>
+        <v>329.67</v>
       </c>
       <c r="G91">
         <v>27.3</v>
@@ -8743,37 +8743,37 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M91">
-        <v>47.85782760000001</v>
+        <v>48.39555600000001</v>
       </c>
       <c r="N91">
-        <v>-7.146716488888899</v>
+        <v>-7.684444888888898</v>
       </c>
       <c r="O91">
-        <v>-1.715211957333336</v>
+        <v>-1.844266773333335</v>
       </c>
       <c r="P91">
-        <v>-5.431504531555563</v>
+        <v>-5.840178115555562</v>
       </c>
       <c r="Q91">
-        <v>4.968495468444435</v>
+        <v>4.559821884444436</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4969344818512712</v>
+        <v>0.5420479300363983</v>
       </c>
       <c r="T91">
-        <v>9.275799774131409</v>
+        <v>10.20337975154455</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2041602629423711</v>
+        <v>0.2018918155763448</v>
       </c>
       <c r="W91">
-        <v>0.1168292734000599</v>
+        <v>0.1171622814733926</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8506677622598795</v>
+        <v>0.8412158982347698</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1596508463296932</v>
+        <v>0.1606608463296932</v>
       </c>
       <c r="C92">
-        <v>-142.7403360987722</v>
+        <v>-147.8069994504897</v>
       </c>
       <c r="D92">
-        <v>159.6296639012278</v>
+        <v>158.2260005495104</v>
       </c>
       <c r="E92">
-        <v>186.37</v>
+        <v>190.033</v>
       </c>
       <c r="F92">
-        <v>329.67</v>
+        <v>333.333</v>
       </c>
       <c r="G92">
         <v>27.3</v>
@@ -8825,37 +8825,37 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M92">
-        <v>48.39555600000001</v>
+        <v>48.93328440000001</v>
       </c>
       <c r="N92">
-        <v>-7.684444888888898</v>
+        <v>-8.222173288888897</v>
       </c>
       <c r="O92">
-        <v>-1.844266773333335</v>
+        <v>-1.973321589333335</v>
       </c>
       <c r="P92">
-        <v>-5.840178115555562</v>
+        <v>-6.248851699555561</v>
       </c>
       <c r="Q92">
-        <v>4.559821884444436</v>
+        <v>4.151148300444437</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5420479300363983</v>
+        <v>0.5971865889293315</v>
       </c>
       <c r="T92">
-        <v>10.20337975154455</v>
+        <v>11.33708861282728</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2018918155763448</v>
+        <v>0.1996732241963849</v>
       </c>
       <c r="W92">
-        <v>0.1171622814733926</v>
+        <v>0.1174879706879707</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8412158982347698</v>
+        <v>0.8319717674849372</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1606608463296932</v>
+        <v>0.1616708463296932</v>
       </c>
       <c r="C93">
-        <v>-147.8069994504897</v>
+        <v>-152.8491924538815</v>
       </c>
       <c r="D93">
-        <v>158.2260005495104</v>
+        <v>156.8468075461185</v>
       </c>
       <c r="E93">
-        <v>190.033</v>
+        <v>193.696</v>
       </c>
       <c r="F93">
-        <v>333.333</v>
+        <v>336.996</v>
       </c>
       <c r="G93">
         <v>27.3</v>
@@ -8907,37 +8907,37 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M93">
-        <v>48.93328440000001</v>
+        <v>49.47101280000001</v>
       </c>
       <c r="N93">
-        <v>-8.222173288888897</v>
+        <v>-8.759901688888903</v>
       </c>
       <c r="O93">
-        <v>-1.973321589333335</v>
+        <v>-2.102376405333337</v>
       </c>
       <c r="P93">
-        <v>-6.248851699555561</v>
+        <v>-6.657525283555566</v>
       </c>
       <c r="Q93">
-        <v>4.151148300444437</v>
+        <v>3.742474716444432</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5971865889293315</v>
+        <v>0.6661099125454981</v>
       </c>
       <c r="T93">
-        <v>11.33708861282728</v>
+        <v>12.75422468943069</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1996732241963849</v>
+        <v>0.1975028630638155</v>
       </c>
       <c r="W93">
-        <v>0.1174879706879707</v>
+        <v>0.1178065797022319</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8319717674849372</v>
+        <v>0.8229285960992312</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1616708463296932</v>
+        <v>0.1626808463296932</v>
       </c>
       <c r="C94">
-        <v>-152.8491924538815</v>
+        <v>-157.8675494742673</v>
       </c>
       <c r="D94">
-        <v>156.8468075461185</v>
+        <v>155.4914505257328</v>
       </c>
       <c r="E94">
-        <v>193.696</v>
+        <v>197.359</v>
       </c>
       <c r="F94">
-        <v>336.996</v>
+        <v>340.659</v>
       </c>
       <c r="G94">
         <v>27.3</v>
@@ -8989,37 +8989,37 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M94">
-        <v>49.47101280000001</v>
+        <v>50.00874120000001</v>
       </c>
       <c r="N94">
-        <v>-8.759901688888903</v>
+        <v>-9.297630088888901</v>
       </c>
       <c r="O94">
-        <v>-2.102376405333337</v>
+        <v>-2.231431221333336</v>
       </c>
       <c r="P94">
-        <v>-6.657525283555566</v>
+        <v>-7.066198867555565</v>
       </c>
       <c r="Q94">
-        <v>3.742474716444432</v>
+        <v>3.333801132444433</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6661099125454981</v>
+        <v>0.7547256143377121</v>
       </c>
       <c r="T94">
-        <v>12.75422468943069</v>
+        <v>14.57625678792079</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1975028630638155</v>
+        <v>0.1953791763642046</v>
       </c>
       <c r="W94">
-        <v>0.1178065797022319</v>
+        <v>0.1181183369097348</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8229285960992312</v>
+        <v>0.8140799015175191</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1626808463296932</v>
+        <v>0.1636908463296932</v>
       </c>
       <c r="C95">
-        <v>-157.8675494742673</v>
+        <v>-162.862683137909</v>
       </c>
       <c r="D95">
-        <v>155.4914505257328</v>
+        <v>154.159316862091</v>
       </c>
       <c r="E95">
-        <v>197.359</v>
+        <v>201.022</v>
       </c>
       <c r="F95">
-        <v>340.659</v>
+        <v>344.3220000000001</v>
       </c>
       <c r="G95">
         <v>27.3</v>
@@ -9071,37 +9071,37 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M95">
-        <v>50.00874120000001</v>
+        <v>50.54646960000002</v>
       </c>
       <c r="N95">
-        <v>-9.297630088888901</v>
+        <v>-9.835358488888907</v>
       </c>
       <c r="O95">
-        <v>-2.231431221333336</v>
+        <v>-2.360486037333338</v>
       </c>
       <c r="P95">
-        <v>-7.066198867555565</v>
+        <v>-7.474872451555569</v>
       </c>
       <c r="Q95">
-        <v>3.333801132444433</v>
+        <v>2.925127548444429</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7547256143377121</v>
+        <v>0.8728798833939978</v>
       </c>
       <c r="T95">
-        <v>14.57625678792079</v>
+        <v>17.00563291924093</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1953791763642046</v>
+        <v>0.1933006744879896</v>
       </c>
       <c r="W95">
-        <v>0.1181183369097348</v>
+        <v>0.1184234609851631</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8140799015175191</v>
+        <v>0.8054194770332901</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1636908463296932</v>
+        <v>0.2189641682212101</v>
       </c>
       <c r="C96">
-        <v>-162.862683137909</v>
+        <v>-215.7327311722899</v>
       </c>
       <c r="D96">
-        <v>154.159316862091</v>
+        <v>104.9522688277101</v>
       </c>
       <c r="E96">
-        <v>201.022</v>
+        <v>204.685</v>
       </c>
       <c r="F96">
-        <v>344.3220000000001</v>
+        <v>347.985</v>
       </c>
       <c r="G96">
         <v>27.3</v>
@@ -9153,45 +9153,45 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M96">
-        <v>50.54646960000002</v>
+        <v>69.875388</v>
       </c>
       <c r="N96">
-        <v>-9.835358488888907</v>
+        <v>-29.16427688888889</v>
       </c>
       <c r="O96">
-        <v>-2.360486037333338</v>
+        <v>-6.999426453333334</v>
       </c>
       <c r="P96">
-        <v>-7.474872451555569</v>
+        <v>-22.16485043555556</v>
       </c>
       <c r="Q96">
-        <v>2.925127548444429</v>
+        <v>-11.76485043555556</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8728798833939978</v>
+        <v>1.097562297903137</v>
       </c>
       <c r="T96">
-        <v>17.00563291924093</v>
+        <v>21.62533984388753</v>
       </c>
       <c r="U96">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1933006744879896</v>
+        <v>0.1398298735266653</v>
       </c>
       <c r="W96">
-        <v>0.1184234609851631</v>
+        <v>0.1727221613958456</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.8054194770332901</v>
+        <v>0.5826244730277721</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2189641682212101</v>
+        <v>0.2205141682212101</v>
       </c>
       <c r="C97">
-        <v>-215.7327311722899</v>
+        <v>-220.3268291956453</v>
       </c>
       <c r="D97">
-        <v>104.9522688277101</v>
+        <v>104.0211708043547</v>
       </c>
       <c r="E97">
-        <v>204.685</v>
+        <v>208.348</v>
       </c>
       <c r="F97">
-        <v>347.985</v>
+        <v>351.648</v>
       </c>
       <c r="G97">
         <v>27.3</v>
@@ -9235,37 +9235,37 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M97">
-        <v>69.875388</v>
+        <v>70.6109184</v>
       </c>
       <c r="N97">
-        <v>-29.16427688888889</v>
+        <v>-29.89980728888889</v>
       </c>
       <c r="O97">
-        <v>-6.999426453333334</v>
+        <v>-7.175953749333335</v>
       </c>
       <c r="P97">
-        <v>-22.16485043555556</v>
+        <v>-22.72385353955556</v>
       </c>
       <c r="Q97">
-        <v>-11.76485043555556</v>
+        <v>-12.32385353955556</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.097562297903137</v>
+        <v>1.360502872378922</v>
       </c>
       <c r="T97">
-        <v>21.62533984388753</v>
+        <v>27.03167480485942</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1398298735266653</v>
+        <v>0.1383733123440959</v>
       </c>
       <c r="W97">
-        <v>0.1727221613958456</v>
+        <v>0.1730146388813056</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5826244730277721</v>
+        <v>0.5765554681003995</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2205141682212101</v>
+        <v>0.2220641682212101</v>
       </c>
       <c r="C98">
-        <v>-220.3268291956453</v>
+        <v>-224.9045517758149</v>
       </c>
       <c r="D98">
-        <v>104.0211708043547</v>
+        <v>103.1064482241851</v>
       </c>
       <c r="E98">
-        <v>208.348</v>
+        <v>212.011</v>
       </c>
       <c r="F98">
-        <v>351.648</v>
+        <v>355.311</v>
       </c>
       <c r="G98">
         <v>27.3</v>
@@ -9317,37 +9317,37 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M98">
-        <v>70.6109184</v>
+        <v>71.3464488</v>
       </c>
       <c r="N98">
-        <v>-29.89980728888889</v>
+        <v>-30.6353376888889</v>
       </c>
       <c r="O98">
-        <v>-7.175953749333335</v>
+        <v>-7.352481045333334</v>
       </c>
       <c r="P98">
-        <v>-22.72385353955556</v>
+        <v>-23.28285664355556</v>
       </c>
       <c r="Q98">
-        <v>-12.32385353955556</v>
+        <v>-12.88285664355556</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.360502872378918</v>
+        <v>1.798737163171891</v>
       </c>
       <c r="T98">
-        <v>27.03167480485935</v>
+        <v>36.0422330731458</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1383733123440959</v>
+        <v>0.1369467833508577</v>
       </c>
       <c r="W98">
-        <v>0.1730146388813056</v>
+        <v>0.1733010859031478</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5765554681003995</v>
+        <v>0.5706115972952406</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2220641682212101</v>
+        <v>0.2236141682212101</v>
       </c>
       <c r="C99">
-        <v>-224.9045517758149</v>
+        <v>-229.4663271453269</v>
       </c>
       <c r="D99">
-        <v>103.1064482241851</v>
+        <v>102.2076728546731</v>
       </c>
       <c r="E99">
-        <v>212.011</v>
+        <v>215.674</v>
       </c>
       <c r="F99">
-        <v>355.311</v>
+        <v>358.974</v>
       </c>
       <c r="G99">
         <v>27.3</v>
@@ -9399,37 +9399,37 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M99">
-        <v>71.3464488</v>
+        <v>72.08197920000001</v>
       </c>
       <c r="N99">
-        <v>-30.6353376888889</v>
+        <v>-31.3708680888889</v>
       </c>
       <c r="O99">
-        <v>-7.352481045333334</v>
+        <v>-7.529008341333335</v>
       </c>
       <c r="P99">
-        <v>-23.28285664355556</v>
+        <v>-23.84185974755556</v>
       </c>
       <c r="Q99">
-        <v>-12.88285664355556</v>
+        <v>-13.44185974755557</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.798737163171891</v>
+        <v>2.675205744757836</v>
       </c>
       <c r="T99">
-        <v>36.0422330731458</v>
+        <v>54.0633496097187</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1369467833508577</v>
+        <v>0.1355493671942163</v>
       </c>
       <c r="W99">
-        <v>0.1733010859031478</v>
+        <v>0.1735816870674014</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5706115972952406</v>
+        <v>0.5647890299759015</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2236141682212101</v>
+        <v>0.2251641682212101</v>
       </c>
       <c r="C100">
-        <v>-229.4663271453269</v>
+        <v>-234.0125687341896</v>
       </c>
       <c r="D100">
-        <v>102.2076728546731</v>
+        <v>101.3244312658104</v>
       </c>
       <c r="E100">
-        <v>215.674</v>
+        <v>219.337</v>
       </c>
       <c r="F100">
-        <v>358.974</v>
+        <v>362.637</v>
       </c>
       <c r="G100">
         <v>27.3</v>
@@ -9481,37 +9481,37 @@
         <v>40.71111111111111</v>
       </c>
       <c r="M100">
-        <v>72.08197920000001</v>
+        <v>72.81750960000001</v>
       </c>
       <c r="N100">
-        <v>-31.3708680888889</v>
+        <v>-32.1063984888889</v>
       </c>
       <c r="O100">
-        <v>-7.529008341333335</v>
+        <v>-7.705535637333336</v>
       </c>
       <c r="P100">
-        <v>-23.84185974755556</v>
+        <v>-24.40086285155557</v>
       </c>
       <c r="Q100">
-        <v>-13.44185974755557</v>
+        <v>-14.00086285155557</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.675205744757836</v>
+        <v>5.304611489515673</v>
       </c>
       <c r="T100">
-        <v>54.0633496097187</v>
+        <v>108.1266992194374</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1355493671942163</v>
+        <v>0.134180181667002</v>
       </c>
       <c r="W100">
-        <v>0.1735816870674014</v>
+        <v>0.173856619521266</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5647890299759015</v>
+        <v>0.5590840902791752</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2251641682212101</v>
-      </c>
-      <c r="C101">
-        <v>-234.0125687341896</v>
-      </c>
-      <c r="D101">
-        <v>101.3244312658104</v>
-      </c>
-      <c r="E101">
-        <v>219.337</v>
-      </c>
-      <c r="F101">
-        <v>362.637</v>
-      </c>
-      <c r="G101">
-        <v>27.3</v>
-      </c>
-      <c r="H101">
-        <v>223</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>51.11111111111111</v>
-      </c>
-      <c r="K101">
-        <v>10.4</v>
-      </c>
-      <c r="L101">
-        <v>40.71111111111111</v>
-      </c>
-      <c r="M101">
-        <v>72.81750960000001</v>
-      </c>
-      <c r="N101">
-        <v>-32.1063984888889</v>
-      </c>
-      <c r="O101">
-        <v>-7.705535637333336</v>
-      </c>
-      <c r="P101">
-        <v>-24.40086285155557</v>
-      </c>
-      <c r="Q101">
-        <v>-14.00086285155557</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.304611489515673</v>
-      </c>
-      <c r="T101">
-        <v>108.1266992194374</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.134180181667002</v>
-      </c>
-      <c r="W101">
-        <v>0.173856619521266</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5590840902791752</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
